--- a/2026-2/UTI.xlsx
+++ b/2026-2/UTI.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB84"/>
+  <dimension ref="A1:AB88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3683,31 +3683,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/53-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5017882</t>
+          <t>5017881</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PROTECCION CATODICA</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0060</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Cambio de ánodos de zinc</t>
+          <t>Limpieza de patio</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1800</v>
+        <v>3500</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
-        <v>30020768</v>
+        <v>30020818</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>46177</v>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" s="3" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
@@ -3763,31 +3763,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/53-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>5017883</t>
+          <t>5017881</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>DEFENSA DE CASCO</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0070</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Desm/mont llantas en casco</t>
+          <t>Evacuacion de residuos</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
-        <v>30020769</v>
+        <v>30020818</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>46177</v>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" s="3" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
@@ -3843,31 +3843,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/53-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5017883</t>
+          <t>5017881</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DEFENSA DE CASCO</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0080</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Cambio de cáncamos de llantas</t>
+          <t>Servicio alquiler grua</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>30020769</v>
+        <v>30020818</v>
       </c>
       <c r="N43" s="3" t="n">
         <v>46177</v>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" s="3" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
@@ -3928,12 +3928,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5017884</t>
+          <t>5017882</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ARBOLADURA</t>
+          <t>PROTECCION CATODICA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3943,11 +3943,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Desm/mont plumas y pinzotes</t>
+          <t>Cambio de ánodos de zinc</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2400</v>
+        <v>1800</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
-        <v>30020800</v>
+        <v>30020768</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>46177</v>
@@ -4008,26 +4008,26 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5017884</t>
+          <t>5017883</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ARBOLADURA</t>
+          <t>DEFENSA DE CASCO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Mantenimiento de cáncamos giratorios</t>
+          <t>Desm/mont llantas en casco</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
-        <v>30020800</v>
+        <v>30020769</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>46177</v>
@@ -4088,26 +4088,26 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>5017884</t>
+          <t>5017883</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ARBOLADURA</t>
+          <t>DEFENSA DE CASCO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Cambio de cáncamos</t>
+          <t>Cambio de cáncamos de llantas</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1320</v>
+        <v>2000</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
-        <v>30020800</v>
+        <v>30020769</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>46177</v>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>5017885</t>
+          <t>5017884</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PUERTAS CORREDIZAS</t>
+          <t>ARBOLADURA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4183,11 +4183,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Manteniemiento a puertas corredizas</t>
+          <t>Desm/mont plumas y pinzotes</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
-        <v>30020801</v>
+        <v>30020800</v>
       </c>
       <c r="N47" s="3" t="n">
         <v>46177</v>
@@ -4248,26 +4248,26 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5017886</t>
+          <t>5017884</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TUBERIA DE ESCAPE</t>
+          <t>ARBOLADURA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Cambio de silenciador y escape de grupos</t>
+          <t>Mantenimiento de cáncamos giratorios</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>14000</v>
+        <v>600</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
-        <v>30020802</v>
+        <v>30020800</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>46177</v>
@@ -4328,26 +4328,26 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>5017887</t>
+          <t>5017884</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BARANDAS</t>
+          <t>ARBOLADURA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Confección de barandas</t>
+          <t>Cambio de cáncamos</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2000</v>
+        <v>1320</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
-        <v>30020803</v>
+        <v>30020800</v>
       </c>
       <c r="N49" s="3" t="n">
         <v>46177</v>
@@ -4408,12 +4408,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>5017888</t>
+          <t>5017885</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>REGISTROS</t>
+          <t>PUERTAS CORREDIZAS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4423,11 +4423,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Cambio a estandar 03 registros</t>
+          <t>Manteniemiento a puertas corredizas</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4000</v>
+        <v>2800</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
-        <v>30020804</v>
+        <v>30020801</v>
       </c>
       <c r="N50" s="3" t="n">
         <v>46177</v>
@@ -4488,26 +4488,26 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5017888</t>
+          <t>5017886</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>REGISTROS</t>
+          <t>TUBERIA DE ESCAPE</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Reparación de 04 registros</t>
+          <t>Cambio de silenciador y escape de grupos</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4800</v>
+        <v>14000</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
-        <v>30020804</v>
+        <v>30020802</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>46177</v>
@@ -4568,12 +4568,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>5017889</t>
+          <t>5017887</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LINEA SUR</t>
+          <t>BARANDAS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4583,11 +4583,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Cambio de cono descarga</t>
+          <t>Confección de barandas</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>30020805</v>
+        <v>30020803</v>
       </c>
       <c r="N52" s="3" t="n">
         <v>46177</v>
@@ -4648,26 +4648,26 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5017889</t>
+          <t>5017888</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LINEA SUR</t>
+          <t>REGISTROS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Confeccion de trampa para la netzch</t>
+          <t>Cambio a estandar 03 registros</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1100</v>
+        <v>4000</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
-        <v>30020805</v>
+        <v>30020804</v>
       </c>
       <c r="N53" s="3" t="n">
         <v>46177</v>
@@ -4728,26 +4728,26 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>5017890</t>
+          <t>5017888</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CASETA</t>
+          <t>REGISTROS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Cambio de 08 sumideros</t>
+          <t>Reparación de 04 registros</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4000</v>
+        <v>4800</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
-        <v>30020806</v>
+        <v>30020804</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>46177</v>
@@ -4808,26 +4808,26 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>5017890</t>
+          <t>5017889</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CASETA</t>
+          <t>LINEA SUR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sellado de 02 ventanas</t>
+          <t>Cambio de cono descarga</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>400</v>
+        <v>1800</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
-        <v>30020806</v>
+        <v>30020805</v>
       </c>
       <c r="N55" s="3" t="n">
         <v>46177</v>
@@ -4888,26 +4888,26 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5017890</t>
+          <t>5017889</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CASETA</t>
+          <t>LINEA SUR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Confección de protector de contómetro</t>
+          <t>Confeccion de trampa para la netzch</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
-        <v>30020806</v>
+        <v>30020805</v>
       </c>
       <c r="N56" s="3" t="n">
         <v>46177</v>
@@ -4978,16 +4978,16 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Modifcación de base bba 125-315</t>
+          <t>Cambio de 08 sumideros</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -5048,22 +5048,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>5017891</t>
+          <t>5017890</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FRANCOBORDO</t>
+          <t>CASETA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Cambio de francobordo</t>
+          <t>Sellado de 02 ventanas</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -5077,7 +5077,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
-        <v>30020807</v>
+        <v>30020806</v>
       </c>
       <c r="N58" s="3" t="n">
         <v>46177</v>
@@ -5128,26 +5128,26 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>5017892</t>
+          <t>5017890</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SISTEMA DE ENFRIAMIENTO</t>
+          <t>CASETA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Apert/cierre de ventanas en canaletas</t>
+          <t>Confección de protector de contómetro</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3600</v>
+        <v>1000</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
-        <v>30020808</v>
+        <v>30020806</v>
       </c>
       <c r="N59" s="3" t="n">
         <v>46177</v>
@@ -5208,26 +5208,26 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>5017893</t>
+          <t>5017890</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PRUEBAS ESTANCAS</t>
+          <t>CASETA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0040</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Pruebas estancas</t>
+          <t>Modifcación de base bba 125-315</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
-        <v>30020809</v>
+        <v>30020806</v>
       </c>
       <c r="N60" s="3" t="n">
         <v>46177</v>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>5017894</t>
+          <t>5017891</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SOPORTE TUB DESFOGUE</t>
+          <t>FRANCOBORDO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5303,11 +5303,11 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Cambio de soporte de tub desfogue</t>
+          <t>Cambio de francobordo</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
-        <v>30020810</v>
+        <v>30020807</v>
       </c>
       <c r="N61" s="3" t="n">
         <v>46177</v>
@@ -5368,12 +5368,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>5017895</t>
+          <t>5017892</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TQS PETROLEO</t>
+          <t>SISTEMA DE ENFRIAMIENTO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5383,11 +5383,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Mant de 02 tqs petróleo</t>
+          <t>Apert/cierre de ventanas en canaletas</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2000</v>
+        <v>3600</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
-        <v>30020811</v>
+        <v>30020808</v>
       </c>
       <c r="N62" s="3" t="n">
         <v>46177</v>
@@ -5448,26 +5448,26 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>5017895</t>
+          <t>5017893</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>TQS PETROLEO</t>
+          <t>PRUEBAS ESTANCAS</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Modificación altura de 01 tq petróleo</t>
+          <t>Pruebas estancas</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
-        <v>30020811</v>
+        <v>30020809</v>
       </c>
       <c r="N63" s="3" t="n">
         <v>46177</v>
@@ -5523,17 +5523,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-3</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>5017896</t>
+          <t>5017894</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CARPINTERIA</t>
+          <t>SOPORTE TUB DESFOGUE</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5543,11 +5543,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Mantenimiento de muebles de cocina</t>
+          <t>Cambio de soporte de tub desfogue</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>23000</v>
+        <v>600</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
-        <v>30020812</v>
+        <v>30020810</v>
       </c>
       <c r="N64" s="3" t="n">
         <v>46177</v>
@@ -5603,17 +5603,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>GO/53-226-SA-1</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>5017897</t>
+          <t>5017895</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TUBERIAS</t>
+          <t>TQS PETROLEO</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5623,11 +5623,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Reubicacion de linea de inyectores lado</t>
+          <t>Mant de 02 tqs petróleo</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6500</v>
+        <v>2000</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
-        <v>30020813</v>
+        <v>30020811</v>
       </c>
       <c r="N65" s="3" t="n">
         <v>46177</v>
@@ -5663,7 +5663,7 @@
       <c r="AA65" t="inlineStr"/>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>SISTEMAS AUXILIARES</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -5683,17 +5683,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>GO/53-226-SA-1</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>5017897</t>
+          <t>5017895</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>TUBERIAS</t>
+          <t>TQS PETROLEO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5703,11 +5703,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Cambio de tuberia keel cooler DOSAN</t>
+          <t>Modificación altura de 01 tq petróleo</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
-        <v>30020813</v>
+        <v>30020811</v>
       </c>
       <c r="N66" s="3" t="n">
         <v>46177</v>
@@ -5743,7 +5743,7 @@
       <c r="AA66" t="inlineStr"/>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>SISTEMAS AUXILIARES</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -5763,31 +5763,31 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>GO/53-226-SA-1</t>
+          <t>GO/53-226-CA-PI-3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>5017897</t>
+          <t>5017896</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>TUBERIAS</t>
+          <t>CARPINTERIA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Confeccion manifold de baldeo lado Sur</t>
+          <t>Mantenimiento de muebles de cocina</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2000</v>
+        <v>23000</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
-        <v>30020813</v>
+        <v>30020812</v>
       </c>
       <c r="N67" s="3" t="n">
         <v>46177</v>
@@ -5823,7 +5823,7 @@
       <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>SISTEMAS AUXILIARES</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -5858,16 +5858,16 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Cambio tuberia de descarga de 2"</t>
+          <t>Reubicacion de linea de inyectores lado</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -5938,16 +5938,16 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Cambio tuberia de baldeo de 6" lado sur</t>
+          <t>Cambio de tuberia keel cooler DOSAN</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -6018,16 +6018,16 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0060</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Cambio tuberia de presion bomba vertical</t>
+          <t>Confeccion manifold de baldeo lado Sur</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2600</v>
+        <v>2000</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -6098,16 +6098,16 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0070</t>
+          <t>0040</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Reubicacion tuberia de ingreso de petrol</t>
+          <t>Cambio tuberia de descarga de 2"</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -6178,16 +6178,16 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0080</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Cambio de columna barometrica</t>
+          <t>Cambio tuberia de baldeo de 6" lado sur</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3200</v>
+        <v>7200</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -6243,31 +6243,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>GO/53-226-PM</t>
+          <t>GO/53-226-SA-1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>5017898</t>
+          <t>5017897</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>TANQUE AGUAS SUCIAS</t>
+          <t>TUBERIAS</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0060</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Instalalacion de tuberias de descarga</t>
+          <t>Cambio tuberia de presion bomba vertical</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
-        <v>30020814</v>
+        <v>30020813</v>
       </c>
       <c r="N73" s="3" t="n">
         <v>46177</v>
@@ -6303,7 +6303,7 @@
       <c r="AA73" t="inlineStr"/>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>PROYECTO MEJORA</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -6323,31 +6323,31 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>GO/53-226-PM</t>
+          <t>GO/53-226-SA-1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>5017898</t>
+          <t>5017897</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>TANQUE AGUAS SUCIAS</t>
+          <t>TUBERIAS</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0070</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Instalacion de tuberias de llenado</t>
+          <t>Reubicacion tuberia de ingreso de petrol</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6000</v>
+        <v>1800</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="n">
-        <v>30020814</v>
+        <v>30020813</v>
       </c>
       <c r="N74" s="3" t="n">
         <v>46177</v>
@@ -6383,7 +6383,7 @@
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>PROYECTO MEJORA</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -6403,27 +6403,27 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>GO/53-226-PM</t>
+          <t>GO/53-226-SA-1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>5017898</t>
+          <t>5017897</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>TANQUE AGUAS SUCIAS</t>
+          <t>TUBERIAS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0080</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Confeccion/Instalacion de base ebba</t>
+          <t>Cambio de columna barometrica</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -6437,7 +6437,7 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
-        <v>30020814</v>
+        <v>30020813</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>46177</v>
@@ -6463,7 +6463,7 @@
       <c r="AA75" t="inlineStr"/>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>PROYECTO MEJORA</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -6488,12 +6488,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>5017899</t>
+          <t>5017898</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>TANQUE MEZCLAS OLEOSAS</t>
+          <t>TANQUE AGUAS SUCIAS</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6503,11 +6503,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Confeccion de tanque de mezclas oleosas</t>
+          <t>Instalalacion de tuberias de descarga</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6000</v>
+        <v>2500</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
-        <v>30020815</v>
+        <v>30020814</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>46177</v>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>5017899</t>
+          <t>5017898</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>TANQUE MEZCLAS OLEOSAS</t>
+          <t>TANQUE AGUAS SUCIAS</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6583,11 +6583,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Instalalacion de tuberias de descarga</t>
+          <t>Instalacion de tuberias de llenado</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2500</v>
+        <v>6000</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
-        <v>30020815</v>
+        <v>30020814</v>
       </c>
       <c r="N77" s="3" t="n">
         <v>46177</v>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>5017899</t>
+          <t>5017898</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>TANQUE MEZCLAS OLEOSAS</t>
+          <t>TANQUE AGUAS SUCIAS</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6663,11 +6663,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Instalacion de tuberias de llenado</t>
+          <t>Confeccion/Instalacion de base ebba</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>6000</v>
+        <v>3200</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
-        <v>30020815</v>
+        <v>30020814</v>
       </c>
       <c r="N78" s="3" t="n">
         <v>46177</v>
@@ -6738,16 +6738,16 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Confeccion/Instalacion de base ebba</t>
+          <t>Confeccion de tanque de mezclas oleosas</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3200</v>
+        <v>6000</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -6803,31 +6803,31 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>GO/53-226-TS-1</t>
+          <t>GO/53-226-PM</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>5017900</t>
+          <t>5017899</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>TRATAMIENTOS</t>
+          <t>TANQUE MEZCLAS OLEOSAS</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Arenado y pintado</t>
+          <t>Instalalacion de tuberias de descarga</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>46000</v>
+        <v>2500</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="n">
-        <v>30020816</v>
+        <v>30020815</v>
       </c>
       <c r="N80" s="3" t="n">
         <v>46177</v>
@@ -6863,7 +6863,7 @@
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>TRATAMIENTO SUPERFICIAL</t>
+          <t>PROYECTO MEJORA</t>
         </is>
       </c>
     </row>
@@ -6883,31 +6883,31 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>GO/53-226-BM</t>
+          <t>GO/53-226-PM</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>5017901</t>
+          <t>5017899</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BOMBAS</t>
+          <t>TANQUE MEZCLAS OLEOSAS</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Confección de base de bomba refrigerac</t>
+          <t>Instalacion de tuberias de llenado</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2400</v>
+        <v>6000</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="n">
-        <v>30020817</v>
+        <v>30020815</v>
       </c>
       <c r="N81" s="3" t="n">
         <v>46177</v>
@@ -6943,7 +6943,7 @@
       <c r="AA81" t="inlineStr"/>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>BOMBAS</t>
+          <t>PROYECTO MEJORA</t>
         </is>
       </c>
     </row>
@@ -6963,31 +6963,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>GO/53-226-BM</t>
+          <t>GO/53-226-PM</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>5017901</t>
+          <t>5017899</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>BOMBAS</t>
+          <t>TANQUE MEZCLAS OLEOSAS</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0040</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Confección de base de bomba autocebante</t>
+          <t>Confeccion/Instalacion de base ebba</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2400</v>
+        <v>3200</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
-        <v>30020817</v>
+        <v>30020815</v>
       </c>
       <c r="N82" s="3" t="n">
         <v>46177</v>
@@ -7023,7 +7023,7 @@
       <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>BOMBAS</t>
+          <t>PROYECTO MEJORA</t>
         </is>
       </c>
     </row>
@@ -7043,31 +7043,31 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>GO/53-226-BM</t>
+          <t>GO/53-226-TS-1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>5017901</t>
+          <t>5017900</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>BOMBAS</t>
+          <t>TRATAMIENTOS</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Inst de bba refrigeracion</t>
+          <t>Arenado y pintado</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1800</v>
+        <v>46000</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
-        <v>30020817</v>
+        <v>30020816</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>46177</v>
@@ -7103,7 +7103,7 @@
       <c r="AA83" t="inlineStr"/>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>BOMBAS</t>
+          <t>TRATAMIENTO SUPERFICIAL</t>
         </is>
       </c>
     </row>
@@ -7138,16 +7138,16 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Inst de bba autocebante</t>
+          <t>Confección de base de bomba refrigerac</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -7187,6 +7187,326 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>0</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>GO/53-226-BM</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>5017901</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>BOMBAS</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Confección de base de bomba autocebante</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>2400</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="n">
+        <v>30020817</v>
+      </c>
+      <c r="N85" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>BOMBAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>0</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>GO/53-226-BM</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>5017901</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>BOMBAS</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Inst de bba refrigeracion</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="n">
+        <v>30020817</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>BOMBAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>0</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>GO/53-226-BM</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>5017901</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>BOMBAS</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Inst de bba autocebante</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="n">
+        <v>30020817</v>
+      </c>
+      <c r="N87" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O87" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>BOMBAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>0</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>GO/53-226-CA-PI-4</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>5017902</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ESFUERZO ADICIONAL</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Esfuerzo adicional</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="n">
+        <v>30020819</v>
+      </c>
+      <c r="N88" s="3" t="n">
+        <v>46178</v>
+      </c>
+      <c r="O88" s="3" t="n">
+        <v>46178</v>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" s="3" t="n">
+        <v>46178</v>
+      </c>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/2026-2/UTI.xlsx
+++ b/2026-2/UTI.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB206"/>
+  <dimension ref="A1:AB220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,10 +807,10 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>34.84999999999999</v>
+        <v>34.85</v>
       </c>
       <c r="Z4" t="n">
-        <v>34.84999999999999</v>
+        <v>34.85</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1295,7 +1295,7 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="n">
-        <v>205.49</v>
+        <v>201.39</v>
       </c>
       <c r="Z10" t="n">
         <v>152.16</v>
@@ -1491,7 +1491,7 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="n">
-        <v>163.81</v>
+        <v>159.71</v>
       </c>
       <c r="Z12" t="n">
         <v>148.87</v>
@@ -1671,10 +1671,10 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>38164.17</v>
+        <v>37959.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>17274.35</v>
+        <v>18546.43</v>
       </c>
       <c r="AA14" t="n">
         <v>5348.346299999999</v>
@@ -1759,7 +1759,7 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
-        <v>527.1899999999999</v>
+        <v>518.99</v>
       </c>
       <c r="Z15" t="n">
         <v>251.84</v>
@@ -1857,7 +1857,7 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
-        <v>163.81</v>
+        <v>159.71</v>
       </c>
       <c r="Z16" t="n">
         <v>148.87</v>
@@ -1955,7 +1955,7 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="n">
-        <v>163.81</v>
+        <v>159.71</v>
       </c>
       <c r="Z17" t="n">
         <v>148.87</v>
@@ -2319,7 +2319,7 @@
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="n">
-        <v>223.33</v>
+        <v>215.13</v>
       </c>
       <c r="Z21" t="n">
         <v>244</v>
@@ -2603,10 +2603,10 @@
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="n">
-        <v>8607.279</v>
+        <v>8594.978999999999</v>
       </c>
       <c r="Z24" t="n">
-        <v>7542.820000000001</v>
+        <v>7542.82</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="n">
-        <v>224.87</v>
+        <v>220.77</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -2779,10 +2779,10 @@
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="n">
-        <v>6328.466</v>
+        <v>6320.266000000001</v>
       </c>
       <c r="Z26" t="n">
-        <v>4866.21</v>
+        <v>4928.97</v>
       </c>
       <c r="AA26" t="n">
         <v>351.2484</v>
@@ -2867,7 +2867,7 @@
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="n">
-        <v>1664.354</v>
+        <v>1659.384</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="n">
-        <v>730.675</v>
+        <v>726.285</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -3043,10 +3043,10 @@
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="n">
-        <v>4637.321</v>
+        <v>4646.478</v>
       </c>
       <c r="Z29" t="n">
-        <v>1435.12</v>
+        <v>1541.12</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -3141,7 +3141,7 @@
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="n">
-        <v>302.45</v>
+        <v>298.35</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -3239,7 +3239,7 @@
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="n">
-        <v>787.55</v>
+        <v>783.45</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="n">
-        <v>651</v>
+        <v>646.3199999999999</v>
       </c>
       <c r="Z32" t="n">
         <v>148.87</v>
@@ -3415,7 +3415,7 @@
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="n">
-        <v>302.45</v>
+        <v>298.35</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="n">
-        <v>184.73</v>
+        <v>180.63</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -3591,7 +3591,7 @@
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="n">
-        <v>290.41</v>
+        <v>282.21</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -3679,7 +3679,7 @@
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="n">
-        <v>5651.201</v>
+        <v>5626.601</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -3767,7 +3767,7 @@
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="n">
-        <v>501.953</v>
+        <v>497.853</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -3855,7 +3855,7 @@
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="n">
-        <v>220.596</v>
+        <v>216.496</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -3943,7 +3943,7 @@
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
-        <v>311.352</v>
+        <v>307.252</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -4031,7 +4031,7 @@
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="n">
-        <v>647.6609999999999</v>
+        <v>639.461</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="n">
-        <v>600.5650000000001</v>
+        <v>596.465</v>
       </c>
       <c r="Z41" t="n">
         <v>180</v>
@@ -4207,7 +4207,7 @@
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="n">
-        <v>1158.91</v>
+        <v>1150.71</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -4295,7 +4295,7 @@
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="n">
-        <v>727.691</v>
+        <v>719.491</v>
       </c>
       <c r="Z43" t="n">
         <v>370</v>
@@ -4383,7 +4383,7 @@
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
-        <v>361.391</v>
+        <v>357.291</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -4471,10 +4471,10 @@
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="n">
-        <v>647.0989999999999</v>
+        <v>642.999</v>
       </c>
       <c r="Z45" t="n">
-        <v>95</v>
+        <v>136.84</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="n">
-        <v>568.8579999999999</v>
+        <v>564.758</v>
       </c>
       <c r="Z46" t="n">
         <v>103.89</v>
@@ -4647,7 +4647,7 @@
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="n">
-        <v>1707.898</v>
+        <v>1699.698</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -4981,13 +4981,13 @@
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="n">
-        <v>8826.135</v>
+        <v>8840.504999999999</v>
       </c>
       <c r="Z51" t="n">
-        <v>6790.139999999999</v>
+        <v>6821.52</v>
       </c>
       <c r="AA51" t="n">
-        <v>499.2772399999999</v>
+        <v>499.27724</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
@@ -5069,10 +5069,10 @@
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="n">
-        <v>2291.112</v>
+        <v>2103.793</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>784.1600000000001</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -5239,10 +5239,10 @@
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="n">
-        <v>3651.235</v>
+        <v>3658.375</v>
       </c>
       <c r="Z54" t="n">
-        <v>2288.18</v>
+        <v>2379.31</v>
       </c>
       <c r="AA54" t="n">
         <v>121.228</v>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>A.S/0061-226-JC-CE</t>
+          <t>A.S/0061-226-AD-CE</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5573,7 +5573,7 @@
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="n">
-        <v>11205.676</v>
+        <v>11123.676</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -5661,10 +5661,10 @@
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="n">
-        <v>15542.288</v>
+        <v>15431.588</v>
       </c>
       <c r="Z59" t="n">
-        <v>7600.009999999999</v>
+        <v>7600.01</v>
       </c>
       <c r="AA59" t="n">
         <v>1496.8309</v>
@@ -5913,7 +5913,7 @@
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="n">
-        <v>2568.64</v>
+        <v>2560.44</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -6585,7 +6585,7 @@
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="n">
-        <v>277.824</v>
+        <v>273.724</v>
       </c>
       <c r="Z70" t="n">
         <v>139.3</v>
@@ -6845,7 +6845,7 @@
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="n">
-        <v>1588.195</v>
+        <v>1584.095</v>
       </c>
       <c r="Z73" t="n">
         <v>103.89</v>
@@ -7097,7 +7097,7 @@
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="n">
-        <v>804.856</v>
+        <v>800.7560000000001</v>
       </c>
       <c r="Z76" t="n">
         <v>0</v>
@@ -8021,10 +8021,10 @@
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="n">
-        <v>3556.956</v>
+        <v>3594.126</v>
       </c>
       <c r="Z87" t="n">
-        <v>2164.71</v>
+        <v>2206.47</v>
       </c>
       <c r="AA87" t="n">
         <v>127.526</v>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>A.S/0061-226-JC-CE</t>
+          <t>A.S/0061-226-AD-CE</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8565,7 +8565,7 @@
       <c r="W93" t="inlineStr"/>
       <c r="X93" t="inlineStr"/>
       <c r="Y93" t="n">
-        <v>17251.917</v>
+        <v>17153.517</v>
       </c>
       <c r="Z93" t="n">
         <v>17021.94</v>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>A.S/0061-226-JC-CE</t>
+          <t>A.S/0061-226-AD-CE</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8653,10 +8653,10 @@
       <c r="W94" t="inlineStr"/>
       <c r="X94" t="inlineStr"/>
       <c r="Y94" t="n">
-        <v>14353.373</v>
+        <v>14271.373</v>
       </c>
       <c r="Z94" t="n">
-        <v>8916.5</v>
+        <v>9072.82</v>
       </c>
       <c r="AA94" t="n">
         <v>2262.7827</v>
@@ -8905,7 +8905,7 @@
       <c r="W97" t="inlineStr"/>
       <c r="X97" t="inlineStr"/>
       <c r="Y97" t="n">
-        <v>2285.206</v>
+        <v>2384.906</v>
       </c>
       <c r="Z97" t="n">
         <v>140.48</v>
@@ -8993,10 +8993,10 @@
       <c r="W98" t="inlineStr"/>
       <c r="X98" t="inlineStr"/>
       <c r="Y98" t="n">
-        <v>6601.13</v>
+        <v>7538.889999999999</v>
       </c>
       <c r="Z98" t="n">
-        <v>2580.99</v>
+        <v>2730.66</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>DEFENSA DE RED</t>
+          <t>CUBIERTA PPAL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -9081,7 +9081,7 @@
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="n">
-        <v>3710.772</v>
+        <v>3702.572</v>
       </c>
       <c r="Z99" t="n">
         <v>190</v>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>DEFENSA DE RED</t>
+          <t>CUBIERTA PPAL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -9198,22 +9198,22 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>5017971</t>
+          <t>5017970</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SOPORTE ENJARETADO</t>
+          <t>CUBIERTA PPAL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Confección soporte enjaretado</t>
+          <t>Recuperación de bita x cambio de plancha</t>
         </is>
       </c>
       <c r="I101" t="n">
@@ -9227,13 +9227,13 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="n">
-        <v>30020889</v>
+        <v>30020888</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
@@ -9242,9 +9242,11 @@
       </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" s="3" t="n">
-        <v>46192</v>
-      </c>
-      <c r="U101" t="inlineStr"/>
+        <v>46198</v>
+      </c>
+      <c r="U101" s="3" t="n">
+        <v>46198</v>
+      </c>
       <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr"/>
       <c r="X101" t="inlineStr"/>
@@ -9278,26 +9280,26 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>5017972</t>
+          <t>5017970</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ARBOLADURA</t>
+          <t>CUBIERTA PPAL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0040</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Reparación de pluma ppal y tangón</t>
+          <t>Cambio de plataforma de winche ppal</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5700</v>
+        <v>0</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -9307,13 +9309,13 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="n">
-        <v>30020826</v>
+        <v>30020888</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="O102" s="3" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
@@ -9322,9 +9324,11 @@
       </c>
       <c r="S102" t="inlineStr"/>
       <c r="T102" s="3" t="n">
-        <v>46197</v>
-      </c>
-      <c r="U102" t="inlineStr"/>
+        <v>46199</v>
+      </c>
+      <c r="U102" s="3" t="n">
+        <v>46199</v>
+      </c>
       <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr"/>
       <c r="X102" t="inlineStr"/>
@@ -9358,22 +9362,22 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>5017972</t>
+          <t>5017970</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ARBOLADURA</t>
+          <t>CUBIERTA PPAL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Confección de pluma auxiliar</t>
+          <t>Remc de cajon de bita en cbt ppal</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -9387,13 +9391,13 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="n">
-        <v>30020826</v>
+        <v>30020888</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
@@ -9402,9 +9406,11 @@
       </c>
       <c r="S103" t="inlineStr"/>
       <c r="T103" s="3" t="n">
-        <v>46197</v>
-      </c>
-      <c r="U103" t="inlineStr"/>
+        <v>46199</v>
+      </c>
+      <c r="U103" s="3" t="n">
+        <v>46199</v>
+      </c>
       <c r="V103" t="inlineStr"/>
       <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr"/>
@@ -9438,22 +9444,22 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>5017972</t>
+          <t>5017971</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ARBOLADURA</t>
+          <t>SOPORTE ENJARETADO</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Confección base luces de navegación</t>
+          <t>Confección soporte enjaretado</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -9467,13 +9473,13 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="n">
-        <v>30020826</v>
+        <v>30020889</v>
       </c>
       <c r="N104" s="3" t="n">
-        <v>46197</v>
+        <v>46192</v>
       </c>
       <c r="O104" s="3" t="n">
-        <v>46197</v>
+        <v>46192</v>
       </c>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
@@ -9482,7 +9488,7 @@
       </c>
       <c r="S104" t="inlineStr"/>
       <c r="T104" s="3" t="n">
-        <v>46197</v>
+        <v>46192</v>
       </c>
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
@@ -9528,16 +9534,16 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Reubicación de base de bandera</t>
+          <t>Reparación de pluma ppal y tangón</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -9568,9 +9574,15 @@
       <c r="V105" t="inlineStr"/>
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr"/>
-      <c r="Y105" t="inlineStr"/>
-      <c r="Z105" t="inlineStr"/>
-      <c r="AA105" t="inlineStr"/>
+      <c r="Y105" t="n">
+        <v>5168.003</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0</v>
+      </c>
       <c r="AB105" t="inlineStr">
         <is>
           <t>ADITAMENTO</t>
@@ -9593,27 +9605,27 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>A.S/0061-226-AD-CE</t>
+          <t>A.S/0061-226-AD-CA</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>5017975</t>
+          <t>5017972</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>BODEGAS</t>
+          <t>ARBOLADURA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Cambio de pl en mamp long</t>
+          <t>Confección de pluma auxiliar</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -9627,7 +9639,7 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="n">
-        <v>30020827</v>
+        <v>30020826</v>
       </c>
       <c r="N106" s="3" t="n">
         <v>46197</v>
@@ -9648,12 +9660,18 @@
       <c r="V106" t="inlineStr"/>
       <c r="W106" t="inlineStr"/>
       <c r="X106" t="inlineStr"/>
-      <c r="Y106" t="inlineStr"/>
-      <c r="Z106" t="inlineStr"/>
-      <c r="AA106" t="inlineStr"/>
+      <c r="Y106" t="n">
+        <v>6655.796</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0</v>
+      </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>ADITAMENTO</t>
         </is>
       </c>
     </row>
@@ -9673,27 +9691,27 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>A.S/0061-226-AD-CE</t>
+          <t>A.S/0061-226-AD-CA</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>5017975</t>
+          <t>5017972</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>BODEGAS</t>
+          <t>ARBOLADURA</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Cambio de pl en mamp transv</t>
+          <t>Confección base luces de navegación</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -9707,7 +9725,7 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="n">
-        <v>30020827</v>
+        <v>30020826</v>
       </c>
       <c r="N107" s="3" t="n">
         <v>46197</v>
@@ -9733,7 +9751,7 @@
       <c r="AA107" t="inlineStr"/>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>ADITAMENTO</t>
         </is>
       </c>
     </row>
@@ -9753,27 +9771,27 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>A.S/0061-226-AD-1</t>
+          <t>A.S/0061-226-AD-CA</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>5017976</t>
+          <t>5017972</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>PROPULSION</t>
+          <t>ARBOLADURA</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0040</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Reparación de propulsión</t>
+          <t>Reubicación de base de bandera</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -9787,7 +9805,7 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="n">
-        <v>30020828</v>
+        <v>30020826</v>
       </c>
       <c r="N108" s="3" t="n">
         <v>46197</v>
@@ -9804,30 +9822,22 @@
       <c r="T108" s="3" t="n">
         <v>46197</v>
       </c>
-      <c r="U108" s="3" t="n">
-        <v>46197</v>
-      </c>
+      <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" t="inlineStr"/>
       <c r="X108" t="inlineStr"/>
-      <c r="Y108" t="n">
-        <v>33070.44</v>
-      </c>
-      <c r="Z108" t="n">
-        <v>32690.8</v>
-      </c>
-      <c r="AA108" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y108" t="inlineStr"/>
+      <c r="Z108" t="inlineStr"/>
+      <c r="AA108" t="inlineStr"/>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>ADITAMENTO</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -9841,71 +9851,59 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>A.S/0061-226-AD-LI</t>
+          <t>A.S/0061-226-AD-CA</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>5017978</t>
+          <t>5017972</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LIMPIEZA</t>
+          <t>ARBOLADURA</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2° Limpieza de sala de máquinas</t>
+          <t>Serv maquinado de pines de pinzote</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>543.36</v>
+        <v>0</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
           <t>PEN</t>
         </is>
       </c>
-      <c r="K109" t="n">
-        <v>2060671352</v>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>MULTISERVICIOS KALEB S.A.C.</t>
-        </is>
-      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
-        <v>30020829</v>
+        <v>30020826</v>
       </c>
       <c r="N109" s="3" t="n">
-        <v>46190</v>
+        <v>46198</v>
       </c>
       <c r="O109" s="3" t="n">
-        <v>46191</v>
-      </c>
-      <c r="P109" s="3" t="n">
-        <v>46197</v>
-      </c>
+        <v>46198</v>
+      </c>
+      <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="n">
         <v>0</v>
       </c>
       <c r="S109" t="inlineStr"/>
       <c r="T109" s="3" t="n">
-        <v>46197</v>
-      </c>
-      <c r="U109" s="3" t="n">
-        <v>46197</v>
-      </c>
-      <c r="V109" s="3" t="n">
-        <v>46197</v>
-      </c>
+        <v>46198</v>
+      </c>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
       <c r="W109" t="inlineStr"/>
       <c r="X109" t="inlineStr"/>
       <c r="Y109" t="inlineStr"/>
@@ -9913,13 +9911,13 @@
       <c r="AA109" t="inlineStr"/>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>ADITAMENTO</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -9933,71 +9931,59 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>A.S/0061-226-AD-LI</t>
+          <t>A.S/0061-226-AD-CA</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>5017978</t>
+          <t>5017972</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>LIMPIEZA</t>
+          <t>ARBOLADURA</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0060</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2° Limpieza de túnel de propulsión</t>
+          <t>Cambio de bases de equipos electrónicos</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>271.68</v>
+        <v>0</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
           <t>PEN</t>
         </is>
       </c>
-      <c r="K110" t="n">
-        <v>2060671352</v>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>MULTISERVICIOS KALEB S.A.C.</t>
-        </is>
-      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
       <c r="M110" t="n">
-        <v>30020829</v>
+        <v>30020826</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>46193</v>
+        <v>46198</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>46193</v>
-      </c>
-      <c r="P110" s="3" t="n">
-        <v>46197</v>
-      </c>
+        <v>46198</v>
+      </c>
+      <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="n">
         <v>0</v>
       </c>
       <c r="S110" t="inlineStr"/>
       <c r="T110" s="3" t="n">
-        <v>46197</v>
-      </c>
-      <c r="U110" s="3" t="n">
-        <v>46197</v>
-      </c>
-      <c r="V110" s="3" t="n">
-        <v>46197</v>
-      </c>
+        <v>46198</v>
+      </c>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr"/>
@@ -10005,13 +9991,13 @@
       <c r="AA110" t="inlineStr"/>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>ADITAMENTO</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -10025,57 +10011,49 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>A.S/0061-226-AD-LI</t>
+          <t>A.S/0061-226-AD-CE</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>5017978</t>
+          <t>5017975</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>LIMPIEZA</t>
+          <t>BODEGAS</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Trasvase de residos x 2° limpiezas</t>
+          <t>Cambio de pl en mamp long</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>460.84</v>
+        <v>0</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
           <t>PEN</t>
         </is>
       </c>
-      <c r="K111" t="n">
-        <v>2060671352</v>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>MULTISERVICIOS KALEB S.A.C.</t>
-        </is>
-      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
       <c r="M111" t="n">
-        <v>30020829</v>
+        <v>30020827</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>46193</v>
+        <v>46197</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>46195</v>
-      </c>
-      <c r="P111" s="3" t="n">
         <v>46197</v>
       </c>
+      <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="n">
         <v>0</v>
@@ -10085,16 +10063,20 @@
         <v>46197</v>
       </c>
       <c r="U111" s="3" t="n">
-        <v>46197</v>
-      </c>
-      <c r="V111" s="3" t="n">
-        <v>46197</v>
-      </c>
+        <v>46199</v>
+      </c>
+      <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr"/>
       <c r="X111" t="inlineStr"/>
-      <c r="Y111" t="inlineStr"/>
-      <c r="Z111" t="inlineStr"/>
-      <c r="AA111" t="inlineStr"/>
+      <c r="Y111" t="n">
+        <v>4805.57</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>3346.21</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>1144.53</v>
+      </c>
       <c r="AB111" t="inlineStr">
         <is>
           <t>CASCO</t>
@@ -10103,7 +10085,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -10117,57 +10099,49 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>A.S/0061-226-AD-LI</t>
+          <t>A.S/0061-226-AD-CE</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>5017978</t>
+          <t>5017975</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>LIMPIEZA</t>
+          <t>BODEGAS</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Trasvas de aceite hidráulico</t>
+          <t>Cambio de pl en mamp transv</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>460.84</v>
+        <v>0</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
           <t>PEN</t>
         </is>
       </c>
-      <c r="K112" t="n">
-        <v>2060671352</v>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>MULTISERVICIOS KALEB S.A.C.</t>
-        </is>
-      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="n">
-        <v>30020829</v>
+        <v>30020827</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>46191</v>
+        <v>46197</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>46192</v>
-      </c>
-      <c r="P112" s="3" t="n">
         <v>46197</v>
       </c>
+      <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="n">
         <v>0</v>
@@ -10177,16 +10151,20 @@
         <v>46197</v>
       </c>
       <c r="U112" s="3" t="n">
-        <v>46197</v>
-      </c>
-      <c r="V112" s="3" t="n">
-        <v>46197</v>
-      </c>
+        <v>46199</v>
+      </c>
+      <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr"/>
       <c r="X112" t="inlineStr"/>
-      <c r="Y112" t="inlineStr"/>
-      <c r="Z112" t="inlineStr"/>
-      <c r="AA112" t="inlineStr"/>
+      <c r="Y112" t="n">
+        <v>2738.233</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>2050.65</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>710.0325</v>
+      </c>
       <c r="AB112" t="inlineStr">
         <is>
           <t>CASCO</t>
@@ -10195,7 +10173,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -10209,71 +10187,61 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>A.S/0061-226-AD-LI</t>
+          <t>A.S/0061-226-AD-CE</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>5017978</t>
+          <t>5017975</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>LIMPIEZA</t>
+          <t>BODEGAS</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Limpieza de tanq petróleo SM</t>
+          <t>Cambio de cuaderna y ref long en bdgs</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>916.8200000000001</v>
+        <v>0</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
           <t>PEN</t>
         </is>
       </c>
-      <c r="K113" t="n">
-        <v>2060671352</v>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>MULTISERVICIOS KALEB S.A.C.</t>
-        </is>
-      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
       <c r="M113" t="n">
-        <v>30020829</v>
+        <v>30020827</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>46191</v>
+        <v>46199</v>
       </c>
       <c r="O113" s="3" t="n">
-        <v>46191</v>
-      </c>
-      <c r="P113" s="3" t="n">
-        <v>46197</v>
-      </c>
+        <v>46199</v>
+      </c>
+      <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="n">
         <v>0</v>
       </c>
       <c r="S113" t="inlineStr"/>
       <c r="T113" s="3" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="U113" s="3" t="n">
-        <v>46197</v>
-      </c>
-      <c r="V113" s="3" t="n">
-        <v>46197</v>
-      </c>
+        <v>46199</v>
+      </c>
+      <c r="V113" t="inlineStr"/>
       <c r="W113" t="inlineStr"/>
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr"/>
@@ -10291,27 +10259,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CHATA MALABRIGO</t>
+          <t>EP PDA 2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GO/52</t>
+          <t>A.S/0061</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-1</t>
+          <t>A.S/0061-226-AD-1</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>5017860</t>
+          <t>5017976</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>TRABAJOS INICIALES</t>
+          <t>PROPULSION</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -10321,7 +10289,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>VARADA / DESVARADA</t>
+          <t>Reparación de propulsión</t>
         </is>
       </c>
       <c r="I114" t="n">
@@ -10334,12 +10302,14 @@
       </c>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
+      <c r="M114" t="n">
+        <v>30020828</v>
+      </c>
       <c r="N114" s="3" t="n">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
@@ -10348,17 +10318,23 @@
       </c>
       <c r="S114" t="inlineStr"/>
       <c r="T114" s="3" t="n">
-        <v>46176</v>
+        <v>46197</v>
       </c>
       <c r="U114" s="3" t="n">
-        <v>46191</v>
+        <v>46197</v>
       </c>
       <c r="V114" t="inlineStr"/>
       <c r="W114" t="inlineStr"/>
       <c r="X114" t="inlineStr"/>
-      <c r="Y114" t="inlineStr"/>
-      <c r="Z114" t="inlineStr"/>
-      <c r="AA114" t="inlineStr"/>
+      <c r="Y114" t="n">
+        <v>33377.62</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>32690.8</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>0</v>
+      </c>
       <c r="AB114" t="inlineStr">
         <is>
           <t>CASCO</t>
@@ -10371,27 +10347,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CHATA MALABRIGO</t>
+          <t>EP PDA 2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GO/52</t>
+          <t>A.S/0061</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-1</t>
+          <t>A.S/0061-226-AD-1</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>5017860</t>
+          <t>5017976</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>TRABAJOS INICIALES</t>
+          <t>PROPULSION</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -10401,25 +10377,33 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ESTADIA DE LA EMBARCACION</t>
+          <t>Remoción de fibra en ejes</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
           <t>PEN</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
+      <c r="K115" t="n">
+        <v>2060838820</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>MULTISERVICIOS VASQUEZ &amp; JAV E.I.R.</t>
+        </is>
+      </c>
+      <c r="M115" t="n">
+        <v>30020828</v>
+      </c>
       <c r="N115" s="3" t="n">
-        <v>46176</v>
+        <v>46190</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>46176</v>
+        <v>46190</v>
       </c>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
@@ -10428,12 +10412,14 @@
       </c>
       <c r="S115" t="inlineStr"/>
       <c r="T115" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="U115" s="3" t="n">
-        <v>46191</v>
-      </c>
-      <c r="V115" t="inlineStr"/>
+        <v>46198</v>
+      </c>
+      <c r="V115" s="3" t="n">
+        <v>46204</v>
+      </c>
       <c r="W115" t="inlineStr"/>
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr"/>
@@ -10451,27 +10437,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CHATA MALABRIGO</t>
+          <t>EP PDA 2</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GO/52</t>
+          <t>A.S/0061</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-1</t>
+          <t>A.S/0061-226-AD-1</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>5017860</t>
+          <t>5017976</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>TRABAJOS INICIALES</t>
+          <t>PROPULSION</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -10481,7 +10467,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>CALIBRACION</t>
+          <t>Reparación de hélice</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -10489,17 +10475,19 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>PEN</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
+      <c r="M116" t="n">
+        <v>30020828</v>
+      </c>
       <c r="N116" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
@@ -10508,10 +10496,10 @@
       </c>
       <c r="S116" t="inlineStr"/>
       <c r="T116" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="U116" s="3" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="V116" t="inlineStr"/>
       <c r="W116" t="inlineStr"/>
@@ -10531,27 +10519,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CHATA MALABRIGO</t>
+          <t>EP PDA 2</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>GO/52</t>
+          <t>A.S/0061</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-1</t>
+          <t>A.S/0061-226-AD-1</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>5017860</t>
+          <t>5017976</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>TRABAJOS INICIALES</t>
+          <t>PROPULSION</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -10561,11 +10549,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Calderería para varado</t>
+          <t>Remc de bocina mixta</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -10575,13 +10563,13 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="n">
-        <v>30020786</v>
+        <v>30020828</v>
       </c>
       <c r="N117" s="3" t="n">
-        <v>46176</v>
+        <v>46199</v>
       </c>
       <c r="O117" s="3" t="n">
-        <v>46176</v>
+        <v>46199</v>
       </c>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
@@ -10590,17 +10578,23 @@
       </c>
       <c r="S117" t="inlineStr"/>
       <c r="T117" s="3" t="n">
-        <v>46176</v>
+        <v>46199</v>
       </c>
       <c r="U117" s="3" t="n">
-        <v>46191</v>
+        <v>46199</v>
       </c>
       <c r="V117" t="inlineStr"/>
       <c r="W117" t="inlineStr"/>
       <c r="X117" t="inlineStr"/>
-      <c r="Y117" t="inlineStr"/>
-      <c r="Z117" t="inlineStr"/>
-      <c r="AA117" t="inlineStr"/>
+      <c r="Y117" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0</v>
+      </c>
       <c r="AB117" t="inlineStr">
         <is>
           <t>CASCO</t>
@@ -10609,31 +10603,31 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CHATA MALABRIGO</t>
+          <t>EP PDA 2</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>GO/52</t>
+          <t>A.S/0061</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-1</t>
+          <t>A.S/0061-226-AD-LI</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>5017861</t>
+          <t>5017978</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>OTROS SERVICIOS INTERNOS</t>
+          <t>LIMPIEZA</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -10643,39 +10637,51 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>SEGURIDAD INDUSTRIAL</t>
+          <t>2° Limpieza de sala de máquinas</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>543.36</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
           <t>PEN</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
+      <c r="K118" t="n">
+        <v>2060671352</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>MULTISERVICIOS KALEB S.A.C.</t>
+        </is>
+      </c>
+      <c r="M118" t="n">
+        <v>30020829</v>
+      </c>
       <c r="N118" s="3" t="n">
-        <v>46176</v>
+        <v>46190</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>46176</v>
-      </c>
-      <c r="P118" t="inlineStr"/>
+        <v>46191</v>
+      </c>
+      <c r="P118" s="3" t="n">
+        <v>46197</v>
+      </c>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="n">
         <v>0</v>
       </c>
       <c r="S118" t="inlineStr"/>
       <c r="T118" s="3" t="n">
-        <v>46176</v>
+        <v>46197</v>
       </c>
       <c r="U118" s="3" t="n">
-        <v>46191</v>
-      </c>
-      <c r="V118" t="inlineStr"/>
+        <v>46197</v>
+      </c>
+      <c r="V118" s="3" t="n">
+        <v>46197</v>
+      </c>
       <c r="W118" t="inlineStr"/>
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr"/>
@@ -10689,31 +10695,31 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CHATA MALABRIGO</t>
+          <t>EP PDA 2</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GO/52</t>
+          <t>A.S/0061</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-1</t>
+          <t>A.S/0061-226-AD-LI</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>5017861</t>
+          <t>5017978</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>OTROS SERVICIOS INTERNOS</t>
+          <t>LIMPIEZA</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -10723,39 +10729,51 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>LIMPIEZA DE PATIO</t>
+          <t>2° Limpieza de túnel de propulsión</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>271.68</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
           <t>PEN</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
+      <c r="K119" t="n">
+        <v>2060671352</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>MULTISERVICIOS KALEB S.A.C.</t>
+        </is>
+      </c>
+      <c r="M119" t="n">
+        <v>30020829</v>
+      </c>
       <c r="N119" s="3" t="n">
-        <v>46176</v>
+        <v>46193</v>
       </c>
       <c r="O119" s="3" t="n">
-        <v>46176</v>
-      </c>
-      <c r="P119" t="inlineStr"/>
+        <v>46193</v>
+      </c>
+      <c r="P119" s="3" t="n">
+        <v>46197</v>
+      </c>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="n">
         <v>0</v>
       </c>
       <c r="S119" t="inlineStr"/>
       <c r="T119" s="3" t="n">
-        <v>46176</v>
+        <v>46197</v>
       </c>
       <c r="U119" s="3" t="n">
-        <v>46191</v>
-      </c>
-      <c r="V119" t="inlineStr"/>
+        <v>46197</v>
+      </c>
+      <c r="V119" s="3" t="n">
+        <v>46197</v>
+      </c>
       <c r="W119" t="inlineStr"/>
       <c r="X119" t="inlineStr"/>
       <c r="Y119" t="inlineStr"/>
@@ -10769,31 +10787,31 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CHATA MALABRIGO</t>
+          <t>EP PDA 2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>GO/52</t>
+          <t>A.S/0061</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-1</t>
+          <t>A.S/0061-226-AD-LI</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>5017861</t>
+          <t>5017978</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>OTROS SERVICIOS INTERNOS</t>
+          <t>LIMPIEZA</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -10803,39 +10821,51 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>DISPOSICION DE RESIDUOS LIQUIDOS</t>
+          <t>Trasvase de residos x 2° limpiezas</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>460.84</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
           <t>PEN</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
+      <c r="K120" t="n">
+        <v>2060671352</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>MULTISERVICIOS KALEB S.A.C.</t>
+        </is>
+      </c>
+      <c r="M120" t="n">
+        <v>30020829</v>
+      </c>
       <c r="N120" s="3" t="n">
-        <v>46176</v>
+        <v>46193</v>
       </c>
       <c r="O120" s="3" t="n">
-        <v>46176</v>
-      </c>
-      <c r="P120" t="inlineStr"/>
+        <v>46195</v>
+      </c>
+      <c r="P120" s="3" t="n">
+        <v>46197</v>
+      </c>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="n">
         <v>0</v>
       </c>
       <c r="S120" t="inlineStr"/>
       <c r="T120" s="3" t="n">
-        <v>46176</v>
+        <v>46197</v>
       </c>
       <c r="U120" s="3" t="n">
-        <v>46191</v>
-      </c>
-      <c r="V120" t="inlineStr"/>
+        <v>46197</v>
+      </c>
+      <c r="V120" s="3" t="n">
+        <v>46197</v>
+      </c>
       <c r="W120" t="inlineStr"/>
       <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr"/>
@@ -10849,31 +10879,31 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CHATA MALABRIGO</t>
+          <t>EP PDA 2</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>GO/52</t>
+          <t>A.S/0061</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-1</t>
+          <t>A.S/0061-226-AD-LI</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>5017861</t>
+          <t>5017978</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>OTROS SERVICIOS INTERNOS</t>
+          <t>LIMPIEZA</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -10883,39 +10913,51 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>DISPOSICION DE RESIDUOS SOLIDOS</t>
+          <t>Trasvas de aceite hidráulico</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>460.84</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
           <t>PEN</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
+      <c r="K121" t="n">
+        <v>2060671352</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>MULTISERVICIOS KALEB S.A.C.</t>
+        </is>
+      </c>
+      <c r="M121" t="n">
+        <v>30020829</v>
+      </c>
       <c r="N121" s="3" t="n">
-        <v>46176</v>
+        <v>46191</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>46176</v>
-      </c>
-      <c r="P121" t="inlineStr"/>
+        <v>46192</v>
+      </c>
+      <c r="P121" s="3" t="n">
+        <v>46197</v>
+      </c>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="n">
         <v>0</v>
       </c>
       <c r="S121" t="inlineStr"/>
       <c r="T121" s="3" t="n">
-        <v>46176</v>
+        <v>46197</v>
       </c>
       <c r="U121" s="3" t="n">
-        <v>46191</v>
-      </c>
-      <c r="V121" t="inlineStr"/>
+        <v>46197</v>
+      </c>
+      <c r="V121" s="3" t="n">
+        <v>46197</v>
+      </c>
       <c r="W121" t="inlineStr"/>
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr"/>
@@ -10929,31 +10971,31 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CHATA MALABRIGO</t>
+          <t>EP PDA 2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>GO/52</t>
+          <t>A.S/0061</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-1</t>
+          <t>A.S/0061-226-AD-LI</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>5017861</t>
+          <t>5017978</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>OTROS SERVICIOS INTERNOS</t>
+          <t>LIMPIEZA</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -10963,41 +11005,51 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Limpieza de patio</t>
+          <t>Limpieza de tanq petróleo SM</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>5000</v>
+        <v>916.8200000000001</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
           <t>PEN</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
+      <c r="K122" t="n">
+        <v>2060671352</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>MULTISERVICIOS KALEB S.A.C.</t>
+        </is>
+      </c>
       <c r="M122" t="n">
-        <v>30020787</v>
+        <v>30020829</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>46176</v>
+        <v>46191</v>
       </c>
       <c r="O122" s="3" t="n">
-        <v>46176</v>
-      </c>
-      <c r="P122" t="inlineStr"/>
+        <v>46191</v>
+      </c>
+      <c r="P122" s="3" t="n">
+        <v>46197</v>
+      </c>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="n">
         <v>0</v>
       </c>
       <c r="S122" t="inlineStr"/>
       <c r="T122" s="3" t="n">
-        <v>46176</v>
+        <v>46197</v>
       </c>
       <c r="U122" s="3" t="n">
-        <v>46191</v>
-      </c>
-      <c r="V122" t="inlineStr"/>
+        <v>46197</v>
+      </c>
+      <c r="V122" s="3" t="n">
+        <v>46197</v>
+      </c>
       <c r="W122" t="inlineStr"/>
       <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr"/>
@@ -11015,41 +11067,41 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CHATA MALABRIGO</t>
+          <t>EP PDA 2</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>GO/52</t>
+          <t>A.S/0061</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-1</t>
+          <t>A.S/0061-226-AD-CA</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>5017861</t>
+          <t>5017979</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>OTROS SERVICIOS INTERNOS</t>
+          <t>AMURADA</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>0060</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Evacuación de residuos</t>
+          <t>Cambio de 3 gateras en amurada</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -11059,13 +11111,13 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="n">
-        <v>30020787</v>
+        <v>30020894</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="O123" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
@@ -11074,10 +11126,10 @@
       </c>
       <c r="S123" t="inlineStr"/>
       <c r="T123" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="U123" s="3" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="V123" t="inlineStr"/>
       <c r="W123" t="inlineStr"/>
@@ -11087,7 +11139,7 @@
       <c r="AA123" t="inlineStr"/>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>ADITAMENTO</t>
         </is>
       </c>
     </row>
@@ -11097,37 +11149,37 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CHATA MALABRIGO</t>
+          <t>EP PDA 2</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>GO/52</t>
+          <t>A.S/0061</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-1</t>
+          <t>A.S/0061-226-AD-CA</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>5017861</t>
+          <t>5017980</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>OTROS SERVICIOS INTERNOS</t>
+          <t>NUMERO DE CALADOS</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>0070</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>ALQUILER GRUA</t>
+          <t>Confección de número de calados</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -11140,12 +11192,14 @@
       </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
+      <c r="M124" t="n">
+        <v>30020895</v>
+      </c>
       <c r="N124" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
@@ -11154,10 +11208,10 @@
       </c>
       <c r="S124" t="inlineStr"/>
       <c r="T124" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="U124" s="3" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="V124" t="inlineStr"/>
       <c r="W124" t="inlineStr"/>
@@ -11167,7 +11221,7 @@
       <c r="AA124" t="inlineStr"/>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>ADITAMENTO</t>
         </is>
       </c>
     </row>
@@ -11177,41 +11231,41 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CHATA MALABRIGO</t>
+          <t>EP PDA 2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>GO/52</t>
+          <t>A.S/0061</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-1</t>
+          <t>A.S/0061-226-AD-CA</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>5017861</t>
+          <t>5017981</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>OTROS SERVICIOS INTERNOS</t>
+          <t>MATRICULA</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>0080</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Alquiler grua</t>
+          <t>Confección de matrícula ER</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -11221,13 +11275,13 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="n">
-        <v>30020787</v>
+        <v>30020896</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
@@ -11236,10 +11290,10 @@
       </c>
       <c r="S125" t="inlineStr"/>
       <c r="T125" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="U125" s="3" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="V125" t="inlineStr"/>
       <c r="W125" t="inlineStr"/>
@@ -11249,7 +11303,7 @@
       <c r="AA125" t="inlineStr"/>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>ADITAMENTO</t>
         </is>
       </c>
     </row>
@@ -11259,27 +11313,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CHATA MALABRIGO</t>
+          <t>EP PDA 2</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>GO/52</t>
+          <t>A.S/0061</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>GO/52-226-SI-PI-1</t>
+          <t>A.S/0061-226-AD-CA</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>5017862</t>
+          <t>5017982</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>TRABAJOS INICIALES</t>
+          <t>FRANCOBORDO</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -11289,7 +11343,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>ESTADIA DE LA EMBARCACION</t>
+          <t>Cambio marca francobordo</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -11302,12 +11356,14 @@
       </c>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
+      <c r="M126" t="n">
+        <v>30020897</v>
+      </c>
       <c r="N126" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="O126" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
@@ -11316,10 +11372,10 @@
       </c>
       <c r="S126" t="inlineStr"/>
       <c r="T126" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="U126" s="3" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="V126" t="inlineStr"/>
       <c r="W126" t="inlineStr"/>
@@ -11329,7 +11385,7 @@
       <c r="AA126" t="inlineStr"/>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>SINIESTRO</t>
+          <t>ADITAMENTO</t>
         </is>
       </c>
     </row>
@@ -11339,27 +11395,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CHATA MALABRIGO</t>
+          <t>EP PDA 2</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>GO/52</t>
+          <t>A.S/0061</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>GO/52-226-SI-PI-2</t>
+          <t>A.S/0061-226-AD-CA</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>5017864</t>
+          <t>5017983</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SALA DE MAQUINAS</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -11369,11 +11425,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Cambio de pl en casco proa</t>
+          <t>Confección de brazola de mamp SM</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -11383,13 +11439,13 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="n">
-        <v>30020752</v>
+        <v>30020898</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="O127" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr"/>
@@ -11398,10 +11454,10 @@
       </c>
       <c r="S127" t="inlineStr"/>
       <c r="T127" s="3" t="n">
-        <v>46176</v>
+        <v>46198</v>
       </c>
       <c r="U127" s="3" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="V127" t="inlineStr"/>
       <c r="W127" t="inlineStr"/>
@@ -11411,7 +11467,7 @@
       <c r="AA127" t="inlineStr"/>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>SINIESTRO</t>
+          <t>ADITAMENTO</t>
         </is>
       </c>
     </row>
@@ -11431,17 +11487,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-2</t>
+          <t>GO/52-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>5017865</t>
+          <t>5017860</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>TRABAJOS INICIALES</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -11451,11 +11507,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Inst de cuadernas intermedias</t>
+          <t>VARADA / DESVARADA</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -11464,9 +11520,7 @@
       </c>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
-      <c r="M128" t="n">
-        <v>30020753</v>
-      </c>
+      <c r="M128" t="inlineStr"/>
       <c r="N128" s="3" t="n">
         <v>46176</v>
       </c>
@@ -11513,31 +11567,31 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-3</t>
+          <t>GO/52-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>5017866</t>
+          <t>5017860</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ESTRUCTURA MANGUERON</t>
+          <t>TRABAJOS INICIALES</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Confecc de estrucutura de mangueron</t>
+          <t>ESTADIA DE LA EMBARCACION</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>17280</v>
+        <v>0</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -11546,9 +11600,7 @@
       </c>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
-      <c r="M129" t="n">
-        <v>30020754</v>
-      </c>
+      <c r="M129" t="inlineStr"/>
       <c r="N129" s="3" t="n">
         <v>46176</v>
       </c>
@@ -11570,15 +11622,9 @@
       <c r="V129" t="inlineStr"/>
       <c r="W129" t="inlineStr"/>
       <c r="X129" t="inlineStr"/>
-      <c r="Y129" t="n">
-        <v>6301.795999999999</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA129" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y129" t="inlineStr"/>
+      <c r="Z129" t="inlineStr"/>
+      <c r="AA129" t="inlineStr"/>
       <c r="AB129" t="inlineStr">
         <is>
           <t>CASCO</t>
@@ -11601,31 +11647,31 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-3</t>
+          <t>GO/52-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>5017867</t>
+          <t>5017860</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>BITAS</t>
+          <t>TRABAJOS INICIALES</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Instalación de 04 bitas</t>
+          <t>CALIBRACION</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -11634,9 +11680,7 @@
       </c>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
-      <c r="M130" t="n">
-        <v>30020755</v>
-      </c>
+      <c r="M130" t="inlineStr"/>
       <c r="N130" s="3" t="n">
         <v>46176</v>
       </c>
@@ -11683,31 +11727,31 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-3</t>
+          <t>GO/52-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>5017867</t>
+          <t>5017860</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>BITAS</t>
+          <t>TRABAJOS INICIALES</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0040</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Confección/ instalación de 01 bita</t>
+          <t>Calderería para varado</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3200</v>
+        <v>800</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -11717,7 +11761,7 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="n">
-        <v>30020755</v>
+        <v>30020786</v>
       </c>
       <c r="N131" s="3" t="n">
         <v>46176</v>
@@ -11740,15 +11784,9 @@
       <c r="V131" t="inlineStr"/>
       <c r="W131" t="inlineStr"/>
       <c r="X131" t="inlineStr"/>
-      <c r="Y131" t="n">
-        <v>4402.429</v>
-      </c>
-      <c r="Z131" t="n">
-        <v>4250.93</v>
-      </c>
-      <c r="AA131" t="n">
-        <v>829.79793</v>
-      </c>
+      <c r="Y131" t="inlineStr"/>
+      <c r="Z131" t="inlineStr"/>
+      <c r="AA131" t="inlineStr"/>
       <c r="AB131" t="inlineStr">
         <is>
           <t>CASCO</t>
@@ -11771,31 +11809,31 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-3</t>
+          <t>GO/52-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>5017867</t>
+          <t>5017861</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>BITAS</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Instalación lastre en bitas</t>
+          <t>SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -11804,9 +11842,7 @@
       </c>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
-      <c r="M132" t="n">
-        <v>30020755</v>
-      </c>
+      <c r="M132" t="inlineStr"/>
       <c r="N132" s="3" t="n">
         <v>46176</v>
       </c>
@@ -11853,31 +11889,31 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-3</t>
+          <t>GO/52-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>5017867</t>
+          <t>5017861</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>BITAS</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Remc bitas y sellado de cbt</t>
+          <t>LIMPIEZA DE PATIO</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -11886,9 +11922,7 @@
       </c>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
-      <c r="M133" t="n">
-        <v>30020755</v>
-      </c>
+      <c r="M133" t="inlineStr"/>
       <c r="N133" s="3" t="n">
         <v>46176</v>
       </c>
@@ -11935,31 +11969,31 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-3</t>
+          <t>GO/52-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>5017868</t>
+          <t>5017861</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LASTRADO DE TANQUES</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Lastrado de tanques de flotación</t>
+          <t>DISPOSICION DE RESIDUOS LIQUIDOS</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -11968,9 +12002,7 @@
       </c>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
-      <c r="M134" t="n">
-        <v>30020756</v>
-      </c>
+      <c r="M134" t="inlineStr"/>
       <c r="N134" s="3" t="n">
         <v>46176</v>
       </c>
@@ -12017,31 +12049,31 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-2</t>
+          <t>GO/52-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>5017869</t>
+          <t>5017861</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>PRUEBAS ESTANCAS</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0040</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Prueba estanca en tanques de flotación</t>
+          <t>DISPOSICION DE RESIDUOS SOLIDOS</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -12050,9 +12082,7 @@
       </c>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
-      <c r="M135" t="n">
-        <v>30020757</v>
-      </c>
+      <c r="M135" t="inlineStr"/>
       <c r="N135" s="3" t="n">
         <v>46176</v>
       </c>
@@ -12099,31 +12129,31 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-4</t>
+          <t>GO/52-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>5017871</t>
+          <t>5017861</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>TUBERIAS</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Modificación de sistema tuberías</t>
+          <t>Limpieza de patio</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -12133,7 +12163,7 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="n">
-        <v>30020788</v>
+        <v>30020787</v>
       </c>
       <c r="N136" s="3" t="n">
         <v>46176</v>
@@ -12181,31 +12211,31 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-5</t>
+          <t>GO/52-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>5017872</t>
+          <t>5017861</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>ARENADO Y PINTADO</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0060</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Resane en zns quemadas</t>
+          <t>Evacuación de residuos</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4200</v>
+        <v>3000</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -12215,7 +12245,7 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="n">
-        <v>30020789</v>
+        <v>30020787</v>
       </c>
       <c r="N137" s="3" t="n">
         <v>46176</v>
@@ -12263,31 +12293,31 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-5</t>
+          <t>GO/52-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>5017872</t>
+          <t>5017861</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>ARENADO Y PINTADO</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0070</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Enmantado de CHATA</t>
+          <t>ALQUILER GRUA</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -12296,9 +12326,7 @@
       </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
-      <c r="M138" t="n">
-        <v>30020789</v>
-      </c>
+      <c r="M138" t="inlineStr"/>
       <c r="N138" s="3" t="n">
         <v>46176</v>
       </c>
@@ -12345,31 +12373,31 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-5</t>
+          <t>GO/52-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>5017872</t>
+          <t>5017861</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>ARENADO Y PINTADO</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0080</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Hidrolavado de casco OV y OM</t>
+          <t>Alquiler grua</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3388</v>
+        <v>5000</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -12379,7 +12407,7 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="n">
-        <v>30020789</v>
+        <v>30020787</v>
       </c>
       <c r="N139" s="3" t="n">
         <v>46176</v>
@@ -12427,31 +12455,31 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-5</t>
+          <t>GO/52-226-SI-PI-1</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>5017872</t>
+          <t>5017862</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>ARENADO Y PINTADO</t>
+          <t>TRABAJOS INICIALES</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Pintado de casco OV y OM</t>
+          <t>ESTADIA DE LA EMBARCACION</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1386</v>
+        <v>0</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -12460,9 +12488,7 @@
       </c>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
-      <c r="M140" t="n">
-        <v>30020789</v>
-      </c>
+      <c r="M140" t="inlineStr"/>
       <c r="N140" s="3" t="n">
         <v>46176</v>
       </c>
@@ -12489,7 +12515,7 @@
       <c r="AA140" t="inlineStr"/>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SINIESTRO</t>
         </is>
       </c>
     </row>
@@ -12509,31 +12535,31 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-5</t>
+          <t>GO/52-226-SI-PI-2</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>5017872</t>
+          <t>5017864</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>ARENADO Y PINTADO</t>
+          <t>CASCO</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Pintado de interiores</t>
+          <t>Cambio de pl en casco proa</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>8125</v>
+        <v>6000</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -12543,7 +12569,7 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="n">
-        <v>30020789</v>
+        <v>30020752</v>
       </c>
       <c r="N141" s="3" t="n">
         <v>46176</v>
@@ -12571,7 +12597,7 @@
       <c r="AA141" t="inlineStr"/>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SINIESTRO</t>
         </is>
       </c>
     </row>
@@ -12591,17 +12617,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-6</t>
+          <t>GO/52-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>5017873</t>
+          <t>5017865</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>ESFUERZO ADICIONAL</t>
+          <t>CASCO</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -12611,7 +12637,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Esfuerzo adicional</t>
+          <t>Inst de cuadernas intermedias</t>
         </is>
       </c>
       <c r="I142" t="n">
@@ -12625,7 +12651,7 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="n">
-        <v>30020773</v>
+        <v>30020753</v>
       </c>
       <c r="N142" s="3" t="n">
         <v>46176</v>
@@ -12673,17 +12699,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>GO/52-226-CA-PI-5</t>
+          <t>GO/52-226-CA-PI-3</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>5017874</t>
+          <t>5017866</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MISCELANEOS</t>
+          <t>ESTRUCTURA MANGUERON</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -12693,11 +12719,11 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Arenado y pintado de miscelaneos</t>
+          <t>Confecc de estrucutura de mangueron</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3000</v>
+        <v>17280</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -12707,7 +12733,7 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="n">
-        <v>30020774</v>
+        <v>30020754</v>
       </c>
       <c r="N143" s="3" t="n">
         <v>46176</v>
@@ -12730,9 +12756,15 @@
       <c r="V143" t="inlineStr"/>
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr"/>
-      <c r="Y143" t="inlineStr"/>
-      <c r="Z143" t="inlineStr"/>
-      <c r="AA143" t="inlineStr"/>
+      <c r="Y143" t="n">
+        <v>6301.795999999999</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0</v>
+      </c>
       <c r="AB143" t="inlineStr">
         <is>
           <t>CASCO</t>
@@ -12760,12 +12792,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>5017875</t>
+          <t>5017867</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>COLUMNA BAROMETRICA</t>
+          <t>BITAS</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -12775,11 +12807,11 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Cambio columna barometrica</t>
+          <t>Instalación de 04 bitas</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2940</v>
+        <v>7200</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -12789,13 +12821,13 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="n">
-        <v>30020775</v>
+        <v>30020755</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="O144" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
@@ -12804,7 +12836,7 @@
       </c>
       <c r="S144" t="inlineStr"/>
       <c r="T144" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="U144" s="3" t="n">
         <v>46191</v>
@@ -12842,26 +12874,26 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>5017974</t>
+          <t>5017867</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SISTEMA DE VACIO</t>
+          <t>BITAS</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Cambio tub inox desde bba de vacío</t>
+          <t>Confección/ instalación de 01 bita</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>6000</v>
+        <v>3200</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -12871,13 +12903,13 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="n">
-        <v>30020891</v>
+        <v>30020755</v>
       </c>
       <c r="N145" s="3" t="n">
-        <v>46195</v>
+        <v>46176</v>
       </c>
       <c r="O145" s="3" t="n">
-        <v>46195</v>
+        <v>46176</v>
       </c>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
@@ -12886,22 +12918,22 @@
       </c>
       <c r="S145" t="inlineStr"/>
       <c r="T145" s="3" t="n">
-        <v>46195</v>
+        <v>46176</v>
       </c>
       <c r="U145" s="3" t="n">
-        <v>46197</v>
+        <v>46191</v>
       </c>
       <c r="V145" t="inlineStr"/>
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="n">
-        <v>9757.15</v>
+        <v>4402.429</v>
       </c>
       <c r="Z145" t="n">
-        <v>0</v>
+        <v>4250.93</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>829.79793</v>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
@@ -12930,26 +12962,26 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>5017974</t>
+          <t>5017867</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SISTEMA DE VACIO</t>
+          <t>BITAS</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Reparación tub sección-descarga 14" inox</t>
+          <t>Instalación lastre en bitas</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2800</v>
+        <v>2500</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -12959,13 +12991,13 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="n">
-        <v>30020891</v>
+        <v>30020755</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>46195</v>
+        <v>46176</v>
       </c>
       <c r="O146" s="3" t="n">
-        <v>46195</v>
+        <v>46176</v>
       </c>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
@@ -12974,23 +13006,17 @@
       </c>
       <c r="S146" t="inlineStr"/>
       <c r="T146" s="3" t="n">
-        <v>46195</v>
+        <v>46176</v>
       </c>
       <c r="U146" s="3" t="n">
-        <v>46197</v>
+        <v>46191</v>
       </c>
       <c r="V146" t="inlineStr"/>
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr"/>
-      <c r="Y146" t="n">
-        <v>581.23</v>
-      </c>
-      <c r="Z146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA146" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y146" t="inlineStr"/>
+      <c r="Z146" t="inlineStr"/>
+      <c r="AA146" t="inlineStr"/>
       <c r="AB146" t="inlineStr">
         <is>
           <t>CASCO</t>
@@ -13018,26 +13044,26 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>5017974</t>
+          <t>5017867</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SISTEMA DE VACIO</t>
+          <t>BITAS</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0040</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Cambio de 3 manifolds de 6"</t>
+          <t>Remc bitas y sellado de cbt</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>6200</v>
+        <v>6000</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -13047,13 +13073,13 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="n">
-        <v>30020891</v>
+        <v>30020755</v>
       </c>
       <c r="N147" s="3" t="n">
-        <v>46195</v>
+        <v>46176</v>
       </c>
       <c r="O147" s="3" t="n">
-        <v>46195</v>
+        <v>46176</v>
       </c>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
@@ -13062,23 +13088,17 @@
       </c>
       <c r="S147" t="inlineStr"/>
       <c r="T147" s="3" t="n">
-        <v>46195</v>
+        <v>46176</v>
       </c>
       <c r="U147" s="3" t="n">
-        <v>46197</v>
+        <v>46191</v>
       </c>
       <c r="V147" t="inlineStr"/>
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr"/>
-      <c r="Y147" t="n">
-        <v>6925.67</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA147" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y147" t="inlineStr"/>
+      <c r="Z147" t="inlineStr"/>
+      <c r="AA147" t="inlineStr"/>
       <c r="AB147" t="inlineStr">
         <is>
           <t>CASCO</t>
@@ -13091,27 +13111,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CHATA TAMAKUN</t>
+          <t>CHATA MALABRIGO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>GO/53</t>
+          <t>GO/52</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-1</t>
+          <t>GO/52-226-CA-PI-3</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>5017880</t>
+          <t>5017868</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>TRABAJOS INICIALES</t>
+          <t>LASTRADO DE TANQUES</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -13121,11 +13141,11 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>VARADA / DESVARADA</t>
+          <t>Lastrado de tanques de flotación</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -13134,12 +13154,14 @@
       </c>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
+      <c r="M148" t="n">
+        <v>30020756</v>
+      </c>
       <c r="N148" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="O148" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
@@ -13148,9 +13170,11 @@
       </c>
       <c r="S148" t="inlineStr"/>
       <c r="T148" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U148" t="inlineStr"/>
+        <v>46176</v>
+      </c>
+      <c r="U148" s="3" t="n">
+        <v>46191</v>
+      </c>
       <c r="V148" t="inlineStr"/>
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr"/>
@@ -13169,41 +13193,41 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CHATA TAMAKUN</t>
+          <t>CHATA MALABRIGO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>GO/53</t>
+          <t>GO/52</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-1</t>
+          <t>GO/52-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>5017880</t>
+          <t>5017869</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>TRABAJOS INICIALES</t>
+          <t>PRUEBAS ESTANCAS</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>ESTADIA DE LA EMBARCACION</t>
+          <t>Prueba estanca en tanques de flotación</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -13212,12 +13236,14 @@
       </c>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
+      <c r="M149" t="n">
+        <v>30020757</v>
+      </c>
       <c r="N149" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="O149" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
@@ -13226,9 +13252,11 @@
       </c>
       <c r="S149" t="inlineStr"/>
       <c r="T149" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U149" t="inlineStr"/>
+        <v>46176</v>
+      </c>
+      <c r="U149" s="3" t="n">
+        <v>46191</v>
+      </c>
       <c r="V149" t="inlineStr"/>
       <c r="W149" t="inlineStr"/>
       <c r="X149" t="inlineStr"/>
@@ -13247,41 +13275,41 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CHATA TAMAKUN</t>
+          <t>CHATA MALABRIGO</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>GO/53</t>
+          <t>GO/52</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-1</t>
+          <t>GO/52-226-CA-PI-4</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>5017880</t>
+          <t>5017871</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>TRABAJOS INICIALES</t>
+          <t>TUBERIAS</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>CALIBRACION</t>
+          <t>Modificación de sistema tuberías</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -13290,12 +13318,14 @@
       </c>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
+      <c r="M150" t="n">
+        <v>30020788</v>
+      </c>
       <c r="N150" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="O150" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
@@ -13304,21 +13334,17 @@
       </c>
       <c r="S150" t="inlineStr"/>
       <c r="T150" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U150" t="inlineStr"/>
+        <v>46176</v>
+      </c>
+      <c r="U150" s="3" t="n">
+        <v>46191</v>
+      </c>
       <c r="V150" t="inlineStr"/>
       <c r="W150" t="inlineStr"/>
       <c r="X150" t="inlineStr"/>
-      <c r="Y150" t="n">
-        <v>34.85</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA150" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y150" t="inlineStr"/>
+      <c r="Z150" t="inlineStr"/>
+      <c r="AA150" t="inlineStr"/>
       <c r="AB150" t="inlineStr">
         <is>
           <t>CASCO</t>
@@ -13331,27 +13357,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CHATA TAMAKUN</t>
+          <t>CHATA MALABRIGO</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>GO/53</t>
+          <t>GO/52</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-1</t>
+          <t>GO/52-226-CA-PI-5</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>5017881</t>
+          <t>5017872</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>OTROS SERVICIOS INTERNOS</t>
+          <t>ARENADO Y PINTADO</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -13361,11 +13387,11 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>SEGURIDAD INDUSTRIAL</t>
+          <t>Resane en zns quemadas</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -13374,12 +13400,14 @@
       </c>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
+      <c r="M151" t="n">
+        <v>30020789</v>
+      </c>
       <c r="N151" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="O151" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
@@ -13388,9 +13416,11 @@
       </c>
       <c r="S151" t="inlineStr"/>
       <c r="T151" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U151" t="inlineStr"/>
+        <v>46176</v>
+      </c>
+      <c r="U151" s="3" t="n">
+        <v>46191</v>
+      </c>
       <c r="V151" t="inlineStr"/>
       <c r="W151" t="inlineStr"/>
       <c r="X151" t="inlineStr"/>
@@ -13409,27 +13439,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CHATA TAMAKUN</t>
+          <t>CHATA MALABRIGO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>GO/53</t>
+          <t>GO/52</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-1</t>
+          <t>GO/52-226-CA-PI-5</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>5017881</t>
+          <t>5017872</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>OTROS SERVICIOS INTERNOS</t>
+          <t>ARENADO Y PINTADO</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -13439,11 +13469,11 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>LIMPIEZA DE PATIO</t>
+          <t>Enmantado de CHATA</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -13452,12 +13482,14 @@
       </c>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
+      <c r="M152" t="n">
+        <v>30020789</v>
+      </c>
       <c r="N152" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="O152" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
@@ -13466,9 +13498,11 @@
       </c>
       <c r="S152" t="inlineStr"/>
       <c r="T152" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U152" t="inlineStr"/>
+        <v>46176</v>
+      </c>
+      <c r="U152" s="3" t="n">
+        <v>46191</v>
+      </c>
       <c r="V152" t="inlineStr"/>
       <c r="W152" t="inlineStr"/>
       <c r="X152" t="inlineStr"/>
@@ -13487,27 +13521,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CHATA TAMAKUN</t>
+          <t>CHATA MALABRIGO</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>GO/53</t>
+          <t>GO/52</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-1</t>
+          <t>GO/52-226-CA-PI-5</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>5017881</t>
+          <t>5017872</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>OTROS SERVICIOS INTERNOS</t>
+          <t>ARENADO Y PINTADO</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -13517,11 +13551,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>DISPOSICION DE RESIDUOS LIQUIDOS</t>
+          <t>Hidrolavado de casco OV y OM</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>3388</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -13530,12 +13564,14 @@
       </c>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
+      <c r="M153" t="n">
+        <v>30020789</v>
+      </c>
       <c r="N153" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="O153" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
@@ -13544,9 +13580,11 @@
       </c>
       <c r="S153" t="inlineStr"/>
       <c r="T153" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U153" t="inlineStr"/>
+        <v>46176</v>
+      </c>
+      <c r="U153" s="3" t="n">
+        <v>46191</v>
+      </c>
       <c r="V153" t="inlineStr"/>
       <c r="W153" t="inlineStr"/>
       <c r="X153" t="inlineStr"/>
@@ -13565,27 +13603,27 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>CHATA TAMAKUN</t>
+          <t>CHATA MALABRIGO</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>GO/53</t>
+          <t>GO/52</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-1</t>
+          <t>GO/52-226-CA-PI-5</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>5017881</t>
+          <t>5017872</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>OTROS SERVICIOS INTERNOS</t>
+          <t>ARENADO Y PINTADO</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -13595,11 +13633,11 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>DISPOSICION DE RESIDUOS SOLIDOS</t>
+          <t>Pintado de casco OV y OM</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>1386</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -13608,12 +13646,14 @@
       </c>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
+      <c r="M154" t="n">
+        <v>30020789</v>
+      </c>
       <c r="N154" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="O154" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
@@ -13622,9 +13662,11 @@
       </c>
       <c r="S154" t="inlineStr"/>
       <c r="T154" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U154" t="inlineStr"/>
+        <v>46176</v>
+      </c>
+      <c r="U154" s="3" t="n">
+        <v>46191</v>
+      </c>
       <c r="V154" t="inlineStr"/>
       <c r="W154" t="inlineStr"/>
       <c r="X154" t="inlineStr"/>
@@ -13643,27 +13685,27 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CHATA TAMAKUN</t>
+          <t>CHATA MALABRIGO</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>GO/53</t>
+          <t>GO/52</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-1</t>
+          <t>GO/52-226-CA-PI-5</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>5017881</t>
+          <t>5017872</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>OTROS SERVICIOS INTERNOS</t>
+          <t>ARENADO Y PINTADO</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -13673,11 +13715,11 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>SERVICIO DE GRUA</t>
+          <t>Pintado de interiores</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>8125</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -13686,12 +13728,14 @@
       </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
+      <c r="M155" t="n">
+        <v>30020789</v>
+      </c>
       <c r="N155" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="O155" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr"/>
@@ -13700,9 +13744,11 @@
       </c>
       <c r="S155" t="inlineStr"/>
       <c r="T155" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U155" t="inlineStr"/>
+        <v>46176</v>
+      </c>
+      <c r="U155" s="3" t="n">
+        <v>46191</v>
+      </c>
       <c r="V155" t="inlineStr"/>
       <c r="W155" t="inlineStr"/>
       <c r="X155" t="inlineStr"/>
@@ -13721,41 +13767,41 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CHATA TAMAKUN</t>
+          <t>CHATA MALABRIGO</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>GO/53</t>
+          <t>GO/52</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-1</t>
+          <t>GO/52-226-CA-PI-6</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>5017881</t>
+          <t>5017873</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>OTROS SERVICIOS INTERNOS</t>
+          <t>ESFUERZO ADICIONAL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>0060</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Limpieza de patio</t>
+          <t>Esfuerzo adicional</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3500</v>
+        <v>12000</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -13765,13 +13811,13 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="n">
-        <v>30020818</v>
+        <v>30020773</v>
       </c>
       <c r="N156" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="O156" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
@@ -13780,9 +13826,11 @@
       </c>
       <c r="S156" t="inlineStr"/>
       <c r="T156" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="U156" t="inlineStr"/>
+        <v>46176</v>
+      </c>
+      <c r="U156" s="3" t="n">
+        <v>46191</v>
+      </c>
       <c r="V156" t="inlineStr"/>
       <c r="W156" t="inlineStr"/>
       <c r="X156" t="inlineStr"/>
@@ -13801,41 +13849,41 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CHATA TAMAKUN</t>
+          <t>CHATA MALABRIGO</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>GO/53</t>
+          <t>GO/52</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-1</t>
+          <t>GO/52-226-CA-PI-5</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>5017881</t>
+          <t>5017874</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>OTROS SERVICIOS INTERNOS</t>
+          <t>MISCELANEOS</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>0070</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Evacuacion de residuos</t>
+          <t>Arenado y pintado de miscelaneos</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -13845,13 +13893,13 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="n">
-        <v>30020818</v>
+        <v>30020774</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="O157" s="3" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
@@ -13860,9 +13908,11 @@
       </c>
       <c r="S157" t="inlineStr"/>
       <c r="T157" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="U157" t="inlineStr"/>
+        <v>46176</v>
+      </c>
+      <c r="U157" s="3" t="n">
+        <v>46191</v>
+      </c>
       <c r="V157" t="inlineStr"/>
       <c r="W157" t="inlineStr"/>
       <c r="X157" t="inlineStr"/>
@@ -13881,41 +13931,41 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CHATA TAMAKUN</t>
+          <t>CHATA MALABRIGO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>GO/53</t>
+          <t>GO/52</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-1</t>
+          <t>GO/52-226-CA-PI-3</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>5017881</t>
+          <t>5017875</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>OTROS SERVICIOS INTERNOS</t>
+          <t>COLUMNA BAROMETRICA</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>0080</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Servicio alquiler grua</t>
+          <t>Cambio columna barometrica</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>5000</v>
+        <v>2940</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -13925,7 +13975,7 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="n">
-        <v>30020818</v>
+        <v>30020775</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>46177</v>
@@ -13940,9 +13990,11 @@
       </c>
       <c r="S158" t="inlineStr"/>
       <c r="T158" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="U158" t="inlineStr"/>
+        <v>46177</v>
+      </c>
+      <c r="U158" s="3" t="n">
+        <v>46191</v>
+      </c>
       <c r="V158" t="inlineStr"/>
       <c r="W158" t="inlineStr"/>
       <c r="X158" t="inlineStr"/>
@@ -13961,27 +14013,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CHATA TAMAKUN</t>
+          <t>CHATA MALABRIGO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>GO/53</t>
+          <t>GO/52</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/52-226-CA-PI-3</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>5017882</t>
+          <t>5017974</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>PROTECCION CATODICA</t>
+          <t>SISTEMA DE VACIO</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -13991,11 +14043,11 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Cambio de ánodos de zinc</t>
+          <t>Cambio tub inox desde bba de vacío</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1800</v>
+        <v>6000</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -14005,13 +14057,13 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="n">
-        <v>30020768</v>
+        <v>30020891</v>
       </c>
       <c r="N159" s="3" t="n">
-        <v>46177</v>
+        <v>46195</v>
       </c>
       <c r="O159" s="3" t="n">
-        <v>46177</v>
+        <v>46195</v>
       </c>
       <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
@@ -14020,15 +14072,23 @@
       </c>
       <c r="S159" t="inlineStr"/>
       <c r="T159" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U159" t="inlineStr"/>
+        <v>46195</v>
+      </c>
+      <c r="U159" s="3" t="n">
+        <v>46197</v>
+      </c>
       <c r="V159" t="inlineStr"/>
       <c r="W159" t="inlineStr"/>
       <c r="X159" t="inlineStr"/>
-      <c r="Y159" t="inlineStr"/>
-      <c r="Z159" t="inlineStr"/>
-      <c r="AA159" t="inlineStr"/>
+      <c r="Y159" t="n">
+        <v>9757.15</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>0</v>
+      </c>
       <c r="AB159" t="inlineStr">
         <is>
           <t>CASCO</t>
@@ -14041,41 +14101,41 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CHATA TAMAKUN</t>
+          <t>CHATA MALABRIGO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>GO/53</t>
+          <t>GO/52</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/52-226-CA-PI-3</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>5017883</t>
+          <t>5017974</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>DEFENSA DE CASCO</t>
+          <t>SISTEMA DE VACIO</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Desm/mont llantas en casco</t>
+          <t>Reparación tub sección-descarga 14" inox</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -14085,13 +14145,13 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="n">
-        <v>30020769</v>
+        <v>30020891</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>46177</v>
+        <v>46195</v>
       </c>
       <c r="O160" s="3" t="n">
-        <v>46177</v>
+        <v>46195</v>
       </c>
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
@@ -14100,15 +14160,23 @@
       </c>
       <c r="S160" t="inlineStr"/>
       <c r="T160" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U160" t="inlineStr"/>
+        <v>46195</v>
+      </c>
+      <c r="U160" s="3" t="n">
+        <v>46197</v>
+      </c>
       <c r="V160" t="inlineStr"/>
       <c r="W160" t="inlineStr"/>
       <c r="X160" t="inlineStr"/>
-      <c r="Y160" t="inlineStr"/>
-      <c r="Z160" t="inlineStr"/>
-      <c r="AA160" t="inlineStr"/>
+      <c r="Y160" t="n">
+        <v>581.23</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>0</v>
+      </c>
       <c r="AB160" t="inlineStr">
         <is>
           <t>CASCO</t>
@@ -14121,41 +14189,41 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>CHATA TAMAKUN</t>
+          <t>CHATA MALABRIGO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>GO/53</t>
+          <t>GO/52</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/52-226-CA-PI-3</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>5017883</t>
+          <t>5017974</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>DEFENSA DE CASCO</t>
+          <t>SISTEMA DE VACIO</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Cambio de cáncamos de llantas</t>
+          <t>Cambio de 3 manifolds de 6"</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2000</v>
+        <v>6200</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -14165,13 +14233,13 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="n">
-        <v>30020769</v>
+        <v>30020891</v>
       </c>
       <c r="N161" s="3" t="n">
-        <v>46177</v>
+        <v>46195</v>
       </c>
       <c r="O161" s="3" t="n">
-        <v>46177</v>
+        <v>46195</v>
       </c>
       <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr"/>
@@ -14180,15 +14248,23 @@
       </c>
       <c r="S161" t="inlineStr"/>
       <c r="T161" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U161" t="inlineStr"/>
+        <v>46195</v>
+      </c>
+      <c r="U161" s="3" t="n">
+        <v>46197</v>
+      </c>
       <c r="V161" t="inlineStr"/>
       <c r="W161" t="inlineStr"/>
       <c r="X161" t="inlineStr"/>
-      <c r="Y161" t="inlineStr"/>
-      <c r="Z161" t="inlineStr"/>
-      <c r="AA161" t="inlineStr"/>
+      <c r="Y161" t="n">
+        <v>6925.67</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>0</v>
+      </c>
       <c r="AB161" t="inlineStr">
         <is>
           <t>CASCO</t>
@@ -14211,17 +14287,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/53-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>5017884</t>
+          <t>5017880</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ARBOLADURA</t>
+          <t>TRABAJOS INICIALES</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -14231,11 +14307,11 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Desm/mont plumas y pinzotes</t>
+          <t>VARADA / DESVARADA</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -14244,9 +14320,7 @@
       </c>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
-      <c r="M162" t="n">
-        <v>30020800</v>
-      </c>
+      <c r="M162" t="inlineStr"/>
       <c r="N162" s="3" t="n">
         <v>46177</v>
       </c>
@@ -14262,7 +14336,9 @@
       <c r="T162" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U162" t="inlineStr"/>
+      <c r="U162" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V162" t="inlineStr"/>
       <c r="W162" t="inlineStr"/>
       <c r="X162" t="inlineStr"/>
@@ -14291,17 +14367,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/53-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>5017884</t>
+          <t>5017880</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ARBOLADURA</t>
+          <t>TRABAJOS INICIALES</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -14311,11 +14387,11 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Mantenimiento de cáncamos giratorios</t>
+          <t>ESTADIA DE LA EMBARCACION</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -14324,9 +14400,7 @@
       </c>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
-      <c r="M163" t="n">
-        <v>30020800</v>
-      </c>
+      <c r="M163" t="inlineStr"/>
       <c r="N163" s="3" t="n">
         <v>46177</v>
       </c>
@@ -14342,7 +14416,9 @@
       <c r="T163" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U163" t="inlineStr"/>
+      <c r="U163" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V163" t="inlineStr"/>
       <c r="W163" t="inlineStr"/>
       <c r="X163" t="inlineStr"/>
@@ -14371,17 +14447,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/53-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>5017884</t>
+          <t>5017880</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>ARBOLADURA</t>
+          <t>TRABAJOS INICIALES</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -14391,11 +14467,11 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Cambio de cáncamos</t>
+          <t>CALIBRACION</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1320</v>
+        <v>0</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -14404,9 +14480,7 @@
       </c>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
-      <c r="M164" t="n">
-        <v>30020800</v>
-      </c>
+      <c r="M164" t="inlineStr"/>
       <c r="N164" s="3" t="n">
         <v>46177</v>
       </c>
@@ -14422,13 +14496,21 @@
       <c r="T164" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U164" t="inlineStr"/>
+      <c r="U164" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V164" t="inlineStr"/>
       <c r="W164" t="inlineStr"/>
       <c r="X164" t="inlineStr"/>
-      <c r="Y164" t="inlineStr"/>
-      <c r="Z164" t="inlineStr"/>
-      <c r="AA164" t="inlineStr"/>
+      <c r="Y164" t="n">
+        <v>34.85</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>0</v>
+      </c>
       <c r="AB164" t="inlineStr">
         <is>
           <t>CASCO</t>
@@ -14451,17 +14533,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/53-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>5017885</t>
+          <t>5017881</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>PUERTAS CORREDIZAS</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -14471,11 +14553,11 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Manteniemiento a puertas corredizas</t>
+          <t>SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -14484,9 +14566,7 @@
       </c>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
-      <c r="M165" t="n">
-        <v>30020801</v>
-      </c>
+      <c r="M165" t="inlineStr"/>
       <c r="N165" s="3" t="n">
         <v>46177</v>
       </c>
@@ -14502,7 +14582,9 @@
       <c r="T165" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U165" t="inlineStr"/>
+      <c r="U165" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V165" t="inlineStr"/>
       <c r="W165" t="inlineStr"/>
       <c r="X165" t="inlineStr"/>
@@ -14531,17 +14613,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/53-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>5017885</t>
+          <t>5017881</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>PUERTAS CORREDIZAS</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -14551,11 +14633,11 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Confección de puerta corrediza</t>
+          <t>LIMPIEZA DE PATIO</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -14564,14 +14646,12 @@
       </c>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
-      <c r="M166" t="n">
-        <v>30020801</v>
-      </c>
+      <c r="M166" t="inlineStr"/>
       <c r="N166" s="3" t="n">
-        <v>46179</v>
+        <v>46177</v>
       </c>
       <c r="O166" s="3" t="n">
-        <v>46179</v>
+        <v>46177</v>
       </c>
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
@@ -14580,9 +14660,11 @@
       </c>
       <c r="S166" t="inlineStr"/>
       <c r="T166" s="3" t="n">
-        <v>46179</v>
-      </c>
-      <c r="U166" t="inlineStr"/>
+        <v>46177</v>
+      </c>
+      <c r="U166" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V166" t="inlineStr"/>
       <c r="W166" t="inlineStr"/>
       <c r="X166" t="inlineStr"/>
@@ -14611,31 +14693,31 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/53-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>5017886</t>
+          <t>5017881</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>TUBERIA DE ESCAPE</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Cambio de silenciador y escape de grupos</t>
+          <t>DISPOSICION DE RESIDUOS LIQUIDOS</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -14644,9 +14726,7 @@
       </c>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
-      <c r="M167" t="n">
-        <v>30020802</v>
-      </c>
+      <c r="M167" t="inlineStr"/>
       <c r="N167" s="3" t="n">
         <v>46177</v>
       </c>
@@ -14662,7 +14742,9 @@
       <c r="T167" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U167" t="inlineStr"/>
+      <c r="U167" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V167" t="inlineStr"/>
       <c r="W167" t="inlineStr"/>
       <c r="X167" t="inlineStr"/>
@@ -14691,31 +14773,31 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/53-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>5017887</t>
+          <t>5017881</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>BARANDAS</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0040</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Confección de barandas</t>
+          <t>DISPOSICION DE RESIDUOS SOLIDOS</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -14724,9 +14806,7 @@
       </c>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
-      <c r="M168" t="n">
-        <v>30020803</v>
-      </c>
+      <c r="M168" t="inlineStr"/>
       <c r="N168" s="3" t="n">
         <v>46177</v>
       </c>
@@ -14742,7 +14822,9 @@
       <c r="T168" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U168" t="inlineStr"/>
+      <c r="U168" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V168" t="inlineStr"/>
       <c r="W168" t="inlineStr"/>
       <c r="X168" t="inlineStr"/>
@@ -14771,31 +14853,31 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/53-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>5017888</t>
+          <t>5017881</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>REGISTROS</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Cambio a estandar 03 registros</t>
+          <t>SERVICIO DE GRUA</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -14804,9 +14886,7 @@
       </c>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
-      <c r="M169" t="n">
-        <v>30020804</v>
-      </c>
+      <c r="M169" t="inlineStr"/>
       <c r="N169" s="3" t="n">
         <v>46177</v>
       </c>
@@ -14822,7 +14902,9 @@
       <c r="T169" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U169" t="inlineStr"/>
+      <c r="U169" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V169" t="inlineStr"/>
       <c r="W169" t="inlineStr"/>
       <c r="X169" t="inlineStr"/>
@@ -14851,31 +14933,31 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/53-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>5017888</t>
+          <t>5017881</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>REGISTROS</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0060</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Reparación de 04 registros</t>
+          <t>Limpieza de patio</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>4800</v>
+        <v>3500</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -14885,7 +14967,7 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="n">
-        <v>30020804</v>
+        <v>30020818</v>
       </c>
       <c r="N170" s="3" t="n">
         <v>46177</v>
@@ -14900,9 +14982,11 @@
       </c>
       <c r="S170" t="inlineStr"/>
       <c r="T170" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U170" t="inlineStr"/>
+        <v>46178</v>
+      </c>
+      <c r="U170" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V170" t="inlineStr"/>
       <c r="W170" t="inlineStr"/>
       <c r="X170" t="inlineStr"/>
@@ -14931,31 +15015,31 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/53-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>5017889</t>
+          <t>5017881</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>LINEA SUR</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0070</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Cambio de cono descarga</t>
+          <t>Evacuacion de residuos</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1800</v>
+        <v>5000</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -14965,7 +15049,7 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="n">
-        <v>30020805</v>
+        <v>30020818</v>
       </c>
       <c r="N171" s="3" t="n">
         <v>46177</v>
@@ -14980,9 +15064,11 @@
       </c>
       <c r="S171" t="inlineStr"/>
       <c r="T171" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U171" t="inlineStr"/>
+        <v>46178</v>
+      </c>
+      <c r="U171" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V171" t="inlineStr"/>
       <c r="W171" t="inlineStr"/>
       <c r="X171" t="inlineStr"/>
@@ -15011,31 +15097,31 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-2</t>
+          <t>GO/53-226-CA-PI-1</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>5017889</t>
+          <t>5017881</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>LINEA SUR</t>
+          <t>OTROS SERVICIOS INTERNOS</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0080</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Confeccion de trampa para la netzch</t>
+          <t>Servicio alquiler grua</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1100</v>
+        <v>5000</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -15045,7 +15131,7 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="n">
-        <v>30020805</v>
+        <v>30020818</v>
       </c>
       <c r="N172" s="3" t="n">
         <v>46177</v>
@@ -15060,9 +15146,11 @@
       </c>
       <c r="S172" t="inlineStr"/>
       <c r="T172" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U172" t="inlineStr"/>
+        <v>46178</v>
+      </c>
+      <c r="U172" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V172" t="inlineStr"/>
       <c r="W172" t="inlineStr"/>
       <c r="X172" t="inlineStr"/>
@@ -15096,26 +15184,26 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>5017889</t>
+          <t>5017882</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>LINEA SUR</t>
+          <t>PROTECCION CATODICA</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Desmontaje/montaje de tq separador</t>
+          <t>Cambio de ánodos de zinc</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3200</v>
+        <v>1800</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -15125,13 +15213,13 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="n">
-        <v>30020805</v>
+        <v>30020768</v>
       </c>
       <c r="N173" s="3" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="O173" s="3" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
@@ -15140,9 +15228,11 @@
       </c>
       <c r="S173" t="inlineStr"/>
       <c r="T173" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="U173" t="inlineStr"/>
+        <v>46177</v>
+      </c>
+      <c r="U173" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V173" t="inlineStr"/>
       <c r="W173" t="inlineStr"/>
       <c r="X173" t="inlineStr"/>
@@ -15176,26 +15266,26 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>5017889</t>
+          <t>5017883</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>LINEA SUR</t>
+          <t>DEFENSA DE CASCO</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Reforzamiento de cbt</t>
+          <t>Desm/mont llantas en casco</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -15205,13 +15295,13 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="n">
-        <v>30020805</v>
+        <v>30020769</v>
       </c>
       <c r="N174" s="3" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="O174" s="3" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
@@ -15220,9 +15310,11 @@
       </c>
       <c r="S174" t="inlineStr"/>
       <c r="T174" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="U174" t="inlineStr"/>
+        <v>46177</v>
+      </c>
+      <c r="U174" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V174" t="inlineStr"/>
       <c r="W174" t="inlineStr"/>
       <c r="X174" t="inlineStr"/>
@@ -15256,26 +15348,26 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>5017890</t>
+          <t>5017883</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CASETA</t>
+          <t>DEFENSA DE CASCO</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Cambio de 08 sumideros</t>
+          <t>Cambio de cáncamos de llantas</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -15285,7 +15377,7 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="n">
-        <v>30020806</v>
+        <v>30020769</v>
       </c>
       <c r="N175" s="3" t="n">
         <v>46177</v>
@@ -15302,7 +15394,9 @@
       <c r="T175" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U175" t="inlineStr"/>
+      <c r="U175" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V175" t="inlineStr"/>
       <c r="W175" t="inlineStr"/>
       <c r="X175" t="inlineStr"/>
@@ -15336,26 +15430,26 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>5017890</t>
+          <t>5017884</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CASETA</t>
+          <t>ARBOLADURA</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Sellado de 02 ventanas</t>
+          <t>Desm/mont plumas y pinzotes</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>400</v>
+        <v>2400</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -15365,7 +15459,7 @@
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="n">
-        <v>30020806</v>
+        <v>30020800</v>
       </c>
       <c r="N176" s="3" t="n">
         <v>46177</v>
@@ -15382,7 +15476,9 @@
       <c r="T176" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U176" t="inlineStr"/>
+      <c r="U176" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V176" t="inlineStr"/>
       <c r="W176" t="inlineStr"/>
       <c r="X176" t="inlineStr"/>
@@ -15416,26 +15512,26 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>5017890</t>
+          <t>5017884</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CASETA</t>
+          <t>ARBOLADURA</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Confección de protector de contómetro</t>
+          <t>Mantenimiento de cáncamos giratorios</t>
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -15445,7 +15541,7 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="n">
-        <v>30020806</v>
+        <v>30020800</v>
       </c>
       <c r="N177" s="3" t="n">
         <v>46177</v>
@@ -15462,7 +15558,9 @@
       <c r="T177" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U177" t="inlineStr"/>
+      <c r="U177" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V177" t="inlineStr"/>
       <c r="W177" t="inlineStr"/>
       <c r="X177" t="inlineStr"/>
@@ -15496,26 +15594,26 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>5017890</t>
+          <t>5017884</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>CASETA</t>
+          <t>ARBOLADURA</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Modifcación de base bba 125-315</t>
+          <t>Cambio de cáncamos</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2500</v>
+        <v>1320</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -15525,7 +15623,7 @@
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="n">
-        <v>30020806</v>
+        <v>30020800</v>
       </c>
       <c r="N178" s="3" t="n">
         <v>46177</v>
@@ -15542,7 +15640,9 @@
       <c r="T178" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U178" t="inlineStr"/>
+      <c r="U178" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V178" t="inlineStr"/>
       <c r="W178" t="inlineStr"/>
       <c r="X178" t="inlineStr"/>
@@ -15576,12 +15676,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>5017891</t>
+          <t>5017885</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>FRANCOBORDO</t>
+          <t>PUERTAS CORREDIZAS</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -15591,11 +15691,11 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Cambio de francobordo</t>
+          <t>Manteniemiento a puertas corredizas</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>400</v>
+        <v>2800</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -15605,7 +15705,7 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="n">
-        <v>30020807</v>
+        <v>30020801</v>
       </c>
       <c r="N179" s="3" t="n">
         <v>46177</v>
@@ -15622,7 +15722,9 @@
       <c r="T179" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U179" t="inlineStr"/>
+      <c r="U179" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V179" t="inlineStr"/>
       <c r="W179" t="inlineStr"/>
       <c r="X179" t="inlineStr"/>
@@ -15656,26 +15758,26 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>5017892</t>
+          <t>5017885</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SISTEMA DE ENFRIAMIENTO</t>
+          <t>PUERTAS CORREDIZAS</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Apert/cierre de ventanas en canaletas</t>
+          <t>Confección de puerta corrediza</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -15685,13 +15787,13 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="n">
-        <v>30020808</v>
+        <v>30020801</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="O180" s="3" t="n">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="inlineStr"/>
@@ -15700,9 +15802,11 @@
       </c>
       <c r="S180" t="inlineStr"/>
       <c r="T180" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U180" t="inlineStr"/>
+        <v>46179</v>
+      </c>
+      <c r="U180" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V180" t="inlineStr"/>
       <c r="W180" t="inlineStr"/>
       <c r="X180" t="inlineStr"/>
@@ -15736,12 +15840,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>5017893</t>
+          <t>5017886</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>PRUEBAS ESTANCAS</t>
+          <t>TUBERIA DE ESCAPE</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -15751,11 +15855,11 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Pruebas estancas</t>
+          <t>Cambio de silenciador y escape de grupos</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>10000</v>
+        <v>14000</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -15765,7 +15869,7 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="n">
-        <v>30020809</v>
+        <v>30020802</v>
       </c>
       <c r="N181" s="3" t="n">
         <v>46177</v>
@@ -15782,7 +15886,9 @@
       <c r="T181" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U181" t="inlineStr"/>
+      <c r="U181" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V181" t="inlineStr"/>
       <c r="W181" t="inlineStr"/>
       <c r="X181" t="inlineStr"/>
@@ -15816,12 +15922,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>5017894</t>
+          <t>5017887</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>SOPORTE TUB DESFOGUE</t>
+          <t>BARANDAS</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -15831,11 +15937,11 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Cambio de soporte de tub desfogue</t>
+          <t>Confección de barandas</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -15845,7 +15951,7 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="n">
-        <v>30020810</v>
+        <v>30020803</v>
       </c>
       <c r="N182" s="3" t="n">
         <v>46177</v>
@@ -15896,12 +16002,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>5017895</t>
+          <t>5017888</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>TQS PETROLEO</t>
+          <t>REGISTROS</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -15911,11 +16017,11 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Mant de 02 tqs petróleo</t>
+          <t>Cambio a estandar 03 registros</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -15925,7 +16031,7 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="n">
-        <v>30020811</v>
+        <v>30020804</v>
       </c>
       <c r="N183" s="3" t="n">
         <v>46177</v>
@@ -15942,7 +16048,9 @@
       <c r="T183" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U183" t="inlineStr"/>
+      <c r="U183" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V183" t="inlineStr"/>
       <c r="W183" t="inlineStr"/>
       <c r="X183" t="inlineStr"/>
@@ -15976,12 +16084,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>5017895</t>
+          <t>5017888</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>TQS PETROLEO</t>
+          <t>REGISTROS</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -15991,11 +16099,11 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Modificación altura de 01 tq petróleo</t>
+          <t>Reparación de 04 registros</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>500</v>
+        <v>4800</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -16005,7 +16113,7 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="n">
-        <v>30020811</v>
+        <v>30020804</v>
       </c>
       <c r="N184" s="3" t="n">
         <v>46177</v>
@@ -16022,7 +16130,9 @@
       <c r="T184" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U184" t="inlineStr"/>
+      <c r="U184" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V184" t="inlineStr"/>
       <c r="W184" t="inlineStr"/>
       <c r="X184" t="inlineStr"/>
@@ -16051,17 +16161,17 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-3</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>5017896</t>
+          <t>5017889</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>CARPINTERIA</t>
+          <t>LINEA SUR</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -16071,11 +16181,11 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Mantenimiento de muebles de cocina</t>
+          <t>Cambio de cono descarga</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>23000</v>
+        <v>1800</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -16085,7 +16195,7 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="n">
-        <v>30020812</v>
+        <v>30020805</v>
       </c>
       <c r="N185" s="3" t="n">
         <v>46177</v>
@@ -16102,7 +16212,9 @@
       <c r="T185" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U185" t="inlineStr"/>
+      <c r="U185" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V185" t="inlineStr"/>
       <c r="W185" t="inlineStr"/>
       <c r="X185" t="inlineStr"/>
@@ -16131,31 +16243,31 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>GO/53-226-SA-1</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>5017897</t>
+          <t>5017889</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>TUBERIAS</t>
+          <t>LINEA SUR</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Reubicacion de linea de inyectores lado</t>
+          <t>Confeccion de trampa para la netzch</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>6500</v>
+        <v>1100</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -16165,7 +16277,7 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="n">
-        <v>30020813</v>
+        <v>30020805</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>46177</v>
@@ -16182,7 +16294,9 @@
       <c r="T186" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U186" t="inlineStr"/>
+      <c r="U186" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V186" t="inlineStr"/>
       <c r="W186" t="inlineStr"/>
       <c r="X186" t="inlineStr"/>
@@ -16191,7 +16305,7 @@
       <c r="AA186" t="inlineStr"/>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>SISTEMAS AUXILIARES</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -16211,31 +16325,31 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>GO/53-226-SA-1</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>5017897</t>
+          <t>5017889</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>TUBERIAS</t>
+          <t>LINEA SUR</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Cambio de tuberia keel cooler DOSAN</t>
+          <t>Desmontaje/montaje de tq separador</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -16245,13 +16359,13 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="n">
-        <v>30020813</v>
+        <v>30020805</v>
       </c>
       <c r="N187" s="3" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="O187" s="3" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr"/>
@@ -16260,9 +16374,11 @@
       </c>
       <c r="S187" t="inlineStr"/>
       <c r="T187" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U187" t="inlineStr"/>
+        <v>46178</v>
+      </c>
+      <c r="U187" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V187" t="inlineStr"/>
       <c r="W187" t="inlineStr"/>
       <c r="X187" t="inlineStr"/>
@@ -16271,7 +16387,7 @@
       <c r="AA187" t="inlineStr"/>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>SISTEMAS AUXILIARES</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -16291,31 +16407,31 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>GO/53-226-SA-1</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>5017897</t>
+          <t>5017889</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>TUBERIAS</t>
+          <t>LINEA SUR</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0040</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Confeccion manifold de baldeo lado Sur</t>
+          <t>Reforzamiento de cbt</t>
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -16325,13 +16441,13 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="n">
-        <v>30020813</v>
+        <v>30020805</v>
       </c>
       <c r="N188" s="3" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="O188" s="3" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="P188" t="inlineStr"/>
       <c r="Q188" t="inlineStr"/>
@@ -16340,9 +16456,11 @@
       </c>
       <c r="S188" t="inlineStr"/>
       <c r="T188" s="3" t="n">
-        <v>46177</v>
-      </c>
-      <c r="U188" t="inlineStr"/>
+        <v>46178</v>
+      </c>
+      <c r="U188" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V188" t="inlineStr"/>
       <c r="W188" t="inlineStr"/>
       <c r="X188" t="inlineStr"/>
@@ -16351,7 +16469,7 @@
       <c r="AA188" t="inlineStr"/>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>SISTEMAS AUXILIARES</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -16371,31 +16489,31 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>GO/53-226-SA-1</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>5017897</t>
+          <t>5017890</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>TUBERIAS</t>
+          <t>CASETA</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Cambio tuberia de descarga de 2"</t>
+          <t>Cambio de 08 sumideros</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -16405,7 +16523,7 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="n">
-        <v>30020813</v>
+        <v>30020806</v>
       </c>
       <c r="N189" s="3" t="n">
         <v>46177</v>
@@ -16422,7 +16540,9 @@
       <c r="T189" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U189" t="inlineStr"/>
+      <c r="U189" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V189" t="inlineStr"/>
       <c r="W189" t="inlineStr"/>
       <c r="X189" t="inlineStr"/>
@@ -16431,7 +16551,7 @@
       <c r="AA189" t="inlineStr"/>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>SISTEMAS AUXILIARES</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -16451,31 +16571,31 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>GO/53-226-SA-1</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>5017897</t>
+          <t>5017890</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>TUBERIAS</t>
+          <t>CASETA</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Cambio tuberia de baldeo de 6" lado sur</t>
+          <t>Sellado de 02 ventanas</t>
         </is>
       </c>
       <c r="I190" t="n">
-        <v>7200</v>
+        <v>400</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -16485,7 +16605,7 @@
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="n">
-        <v>30020813</v>
+        <v>30020806</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>46177</v>
@@ -16502,7 +16622,9 @@
       <c r="T190" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U190" t="inlineStr"/>
+      <c r="U190" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V190" t="inlineStr"/>
       <c r="W190" t="inlineStr"/>
       <c r="X190" t="inlineStr"/>
@@ -16511,7 +16633,7 @@
       <c r="AA190" t="inlineStr"/>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>SISTEMAS AUXILIARES</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -16531,31 +16653,31 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>GO/53-226-SA-1</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>5017897</t>
+          <t>5017890</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>TUBERIAS</t>
+          <t>CASETA</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>0060</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Cambio tuberia de presion bomba vertical</t>
+          <t>Confección de protector de contómetro</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2600</v>
+        <v>1000</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -16565,7 +16687,7 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="n">
-        <v>30020813</v>
+        <v>30020806</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>46177</v>
@@ -16582,7 +16704,9 @@
       <c r="T191" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U191" t="inlineStr"/>
+      <c r="U191" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V191" t="inlineStr"/>
       <c r="W191" t="inlineStr"/>
       <c r="X191" t="inlineStr"/>
@@ -16591,7 +16715,7 @@
       <c r="AA191" t="inlineStr"/>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>SISTEMAS AUXILIARES</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -16611,31 +16735,31 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>GO/53-226-SA-1</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>5017897</t>
+          <t>5017890</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>TUBERIAS</t>
+          <t>CASETA</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>0070</t>
+          <t>0040</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Reubicacion tuberia de ingreso de petrol</t>
+          <t>Modifcación de base bba 125-315</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1800</v>
+        <v>2500</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -16645,7 +16769,7 @@
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="n">
-        <v>30020813</v>
+        <v>30020806</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>46177</v>
@@ -16662,7 +16786,9 @@
       <c r="T192" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U192" t="inlineStr"/>
+      <c r="U192" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V192" t="inlineStr"/>
       <c r="W192" t="inlineStr"/>
       <c r="X192" t="inlineStr"/>
@@ -16671,7 +16797,7 @@
       <c r="AA192" t="inlineStr"/>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>SISTEMAS AUXILIARES</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -16691,31 +16817,31 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>GO/53-226-SA-1</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>5017897</t>
+          <t>5017891</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>TUBERIAS</t>
+          <t>FRANCOBORDO</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>0080</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Cambio de columna barometrica</t>
+          <t>Cambio de francobordo</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3200</v>
+        <v>400</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -16725,7 +16851,7 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="n">
-        <v>30020813</v>
+        <v>30020807</v>
       </c>
       <c r="N193" s="3" t="n">
         <v>46177</v>
@@ -16742,7 +16868,9 @@
       <c r="T193" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U193" t="inlineStr"/>
+      <c r="U193" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V193" t="inlineStr"/>
       <c r="W193" t="inlineStr"/>
       <c r="X193" t="inlineStr"/>
@@ -16751,7 +16879,7 @@
       <c r="AA193" t="inlineStr"/>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>SISTEMAS AUXILIARES</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -16771,17 +16899,17 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>GO/53-226-PM</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>5017898</t>
+          <t>5017892</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>TANQUE AGUAS SUCIAS</t>
+          <t>SISTEMA DE ENFRIAMIENTO</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -16791,11 +16919,11 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Instalalacion de tuberias de descarga</t>
+          <t>Apert/cierre de ventanas en canaletas</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2500</v>
+        <v>3600</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -16805,7 +16933,7 @@
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="n">
-        <v>30020814</v>
+        <v>30020808</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>46177</v>
@@ -16822,7 +16950,9 @@
       <c r="T194" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U194" t="inlineStr"/>
+      <c r="U194" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V194" t="inlineStr"/>
       <c r="W194" t="inlineStr"/>
       <c r="X194" t="inlineStr"/>
@@ -16831,7 +16961,7 @@
       <c r="AA194" t="inlineStr"/>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>PROYECTO MEJORA</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -16851,31 +16981,31 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>GO/53-226-PM</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>5017898</t>
+          <t>5017893</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>TANQUE AGUAS SUCIAS</t>
+          <t>PRUEBAS ESTANCAS</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Instalacion de tuberias de llenado</t>
+          <t>Pruebas estancas</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -16885,7 +17015,7 @@
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="n">
-        <v>30020814</v>
+        <v>30020809</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>46177</v>
@@ -16902,7 +17032,9 @@
       <c r="T195" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U195" t="inlineStr"/>
+      <c r="U195" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V195" t="inlineStr"/>
       <c r="W195" t="inlineStr"/>
       <c r="X195" t="inlineStr"/>
@@ -16911,7 +17043,7 @@
       <c r="AA195" t="inlineStr"/>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>PROYECTO MEJORA</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -16931,31 +17063,31 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>GO/53-226-PM</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>5017898</t>
+          <t>5017894</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>TANQUE AGUAS SUCIAS</t>
+          <t>SOPORTE TUB DESFOGUE</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Confeccion/Instalacion de base ebba</t>
+          <t>Cambio de soporte de tub desfogue</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3200</v>
+        <v>600</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -16965,7 +17097,7 @@
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="n">
-        <v>30020814</v>
+        <v>30020810</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>46177</v>
@@ -16982,7 +17114,9 @@
       <c r="T196" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U196" t="inlineStr"/>
+      <c r="U196" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V196" t="inlineStr"/>
       <c r="W196" t="inlineStr"/>
       <c r="X196" t="inlineStr"/>
@@ -16991,7 +17125,7 @@
       <c r="AA196" t="inlineStr"/>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>PROYECTO MEJORA</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -17011,17 +17145,17 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>GO/53-226-PM</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>5017899</t>
+          <t>5017895</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>TANQUE MEZCLAS OLEOSAS</t>
+          <t>TQS PETROLEO</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -17031,11 +17165,11 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Confeccion de tanque de mezclas oleosas</t>
+          <t>Mant de 02 tqs petróleo</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -17045,7 +17179,7 @@
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="n">
-        <v>30020815</v>
+        <v>30020811</v>
       </c>
       <c r="N197" s="3" t="n">
         <v>46177</v>
@@ -17062,7 +17196,9 @@
       <c r="T197" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U197" t="inlineStr"/>
+      <c r="U197" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V197" t="inlineStr"/>
       <c r="W197" t="inlineStr"/>
       <c r="X197" t="inlineStr"/>
@@ -17071,7 +17207,7 @@
       <c r="AA197" t="inlineStr"/>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>PROYECTO MEJORA</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -17091,17 +17227,17 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>GO/53-226-PM</t>
+          <t>GO/53-226-CA-PI-2</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>5017899</t>
+          <t>5017895</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>TANQUE MEZCLAS OLEOSAS</t>
+          <t>TQS PETROLEO</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -17111,11 +17247,11 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Instalalacion de tuberias de descarga</t>
+          <t>Modificación altura de 01 tq petróleo</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -17125,7 +17261,7 @@
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
       <c r="M198" t="n">
-        <v>30020815</v>
+        <v>30020811</v>
       </c>
       <c r="N198" s="3" t="n">
         <v>46177</v>
@@ -17142,7 +17278,9 @@
       <c r="T198" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U198" t="inlineStr"/>
+      <c r="U198" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V198" t="inlineStr"/>
       <c r="W198" t="inlineStr"/>
       <c r="X198" t="inlineStr"/>
@@ -17151,7 +17289,7 @@
       <c r="AA198" t="inlineStr"/>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>PROYECTO MEJORA</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -17171,31 +17309,31 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>GO/53-226-PM</t>
+          <t>GO/53-226-CA-PI-3</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>5017899</t>
+          <t>5017896</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>TANQUE MEZCLAS OLEOSAS</t>
+          <t>CARPINTERIA</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Instalacion de tuberias de llenado</t>
+          <t>Mantenimiento de muebles de cocina</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>6000</v>
+        <v>23000</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -17205,7 +17343,7 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="n">
-        <v>30020815</v>
+        <v>30020812</v>
       </c>
       <c r="N199" s="3" t="n">
         <v>46177</v>
@@ -17222,7 +17360,9 @@
       <c r="T199" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U199" t="inlineStr"/>
+      <c r="U199" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V199" t="inlineStr"/>
       <c r="W199" t="inlineStr"/>
       <c r="X199" t="inlineStr"/>
@@ -17231,7 +17371,7 @@
       <c r="AA199" t="inlineStr"/>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>PROYECTO MEJORA</t>
+          <t>CASCO</t>
         </is>
       </c>
     </row>
@@ -17251,31 +17391,31 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>GO/53-226-PM</t>
+          <t>GO/53-226-SA-1</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>5017899</t>
+          <t>5017897</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>TANQUE MEZCLAS OLEOSAS</t>
+          <t>TUBERIAS</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Confeccion/Instalacion de base ebba</t>
+          <t>Reubicacion de linea de inyectores lado</t>
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3200</v>
+        <v>6500</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -17285,7 +17425,7 @@
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="n">
-        <v>30020815</v>
+        <v>30020813</v>
       </c>
       <c r="N200" s="3" t="n">
         <v>46177</v>
@@ -17302,7 +17442,9 @@
       <c r="T200" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U200" t="inlineStr"/>
+      <c r="U200" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V200" t="inlineStr"/>
       <c r="W200" t="inlineStr"/>
       <c r="X200" t="inlineStr"/>
@@ -17311,7 +17453,7 @@
       <c r="AA200" t="inlineStr"/>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>PROYECTO MEJORA</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -17331,31 +17473,31 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>GO/53-226-TS-1</t>
+          <t>GO/53-226-SA-1</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>5017900</t>
+          <t>5017897</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>TRATAMIENTOS</t>
+          <t>TUBERIAS</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Arenado y pintado</t>
+          <t>Cambio de tuberia keel cooler DOSAN</t>
         </is>
       </c>
       <c r="I201" t="n">
-        <v>46000</v>
+        <v>0</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -17365,7 +17507,7 @@
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="n">
-        <v>30020816</v>
+        <v>30020813</v>
       </c>
       <c r="N201" s="3" t="n">
         <v>46177</v>
@@ -17382,7 +17524,9 @@
       <c r="T201" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U201" t="inlineStr"/>
+      <c r="U201" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V201" t="inlineStr"/>
       <c r="W201" t="inlineStr"/>
       <c r="X201" t="inlineStr"/>
@@ -17391,7 +17535,7 @@
       <c r="AA201" t="inlineStr"/>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>TRATAMIENTO SUPERFICIAL</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -17411,31 +17555,31 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>GO/53-226-BM</t>
+          <t>GO/53-226-SA-1</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>5017901</t>
+          <t>5017897</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>BOMBAS</t>
+          <t>TUBERIAS</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Confección de base de bomba refrigerac</t>
+          <t>Confeccion manifold de baldeo lado Sur</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -17445,7 +17589,7 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="n">
-        <v>30020817</v>
+        <v>30020813</v>
       </c>
       <c r="N202" s="3" t="n">
         <v>46177</v>
@@ -17462,7 +17606,9 @@
       <c r="T202" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U202" t="inlineStr"/>
+      <c r="U202" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V202" t="inlineStr"/>
       <c r="W202" t="inlineStr"/>
       <c r="X202" t="inlineStr"/>
@@ -17471,7 +17617,7 @@
       <c r="AA202" t="inlineStr"/>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>BOMBAS</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -17491,31 +17637,31 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>GO/53-226-BM</t>
+          <t>GO/53-226-SA-1</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>5017901</t>
+          <t>5017897</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>BOMBAS</t>
+          <t>TUBERIAS</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0040</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Confección de base de bomba autocebante</t>
+          <t>Cambio tuberia de descarga de 2"</t>
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -17525,7 +17671,7 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="n">
-        <v>30020817</v>
+        <v>30020813</v>
       </c>
       <c r="N203" s="3" t="n">
         <v>46177</v>
@@ -17542,7 +17688,9 @@
       <c r="T203" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U203" t="inlineStr"/>
+      <c r="U203" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V203" t="inlineStr"/>
       <c r="W203" t="inlineStr"/>
       <c r="X203" t="inlineStr"/>
@@ -17551,7 +17699,7 @@
       <c r="AA203" t="inlineStr"/>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>BOMBAS</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -17571,31 +17719,31 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>GO/53-226-BM</t>
+          <t>GO/53-226-SA-1</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>5017901</t>
+          <t>5017897</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>BOMBAS</t>
+          <t>TUBERIAS</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Inst de bba refrigeracion</t>
+          <t>Cambio tuberia de baldeo de 6" lado sur</t>
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1800</v>
+        <v>7200</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -17605,7 +17753,7 @@
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="n">
-        <v>30020817</v>
+        <v>30020813</v>
       </c>
       <c r="N204" s="3" t="n">
         <v>46177</v>
@@ -17622,7 +17770,9 @@
       <c r="T204" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U204" t="inlineStr"/>
+      <c r="U204" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V204" t="inlineStr"/>
       <c r="W204" t="inlineStr"/>
       <c r="X204" t="inlineStr"/>
@@ -17631,7 +17781,7 @@
       <c r="AA204" t="inlineStr"/>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>BOMBAS</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -17651,31 +17801,31 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>GO/53-226-BM</t>
+          <t>GO/53-226-SA-1</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>5017901</t>
+          <t>5017897</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>BOMBAS</t>
+          <t>TUBERIAS</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>0060</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Inst de bba autocebante</t>
+          <t>Cambio tuberia de presion bomba vertical</t>
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1800</v>
+        <v>2600</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -17685,7 +17835,7 @@
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="n">
-        <v>30020817</v>
+        <v>30020813</v>
       </c>
       <c r="N205" s="3" t="n">
         <v>46177</v>
@@ -17702,7 +17852,9 @@
       <c r="T205" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="U205" t="inlineStr"/>
+      <c r="U205" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V205" t="inlineStr"/>
       <c r="W205" t="inlineStr"/>
       <c r="X205" t="inlineStr"/>
@@ -17711,7 +17863,7 @@
       <c r="AA205" t="inlineStr"/>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>BOMBAS</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -17731,31 +17883,31 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>GO/53-226-CA-PI-4</t>
+          <t>GO/53-226-SA-1</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>5017902</t>
+          <t>5017897</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>ESFUERZO ADICIONAL</t>
+          <t>TUBERIAS</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0070</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Esfuerzo adicional</t>
+          <t>Reubicacion tuberia de ingreso de petrol</t>
         </is>
       </c>
       <c r="I206" t="n">
-        <v>8000</v>
+        <v>1800</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -17765,13 +17917,13 @@
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="n">
-        <v>30020819</v>
+        <v>30020813</v>
       </c>
       <c r="N206" s="3" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="O206" s="3" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="P206" t="inlineStr"/>
       <c r="Q206" t="inlineStr"/>
@@ -17780,9 +17932,11 @@
       </c>
       <c r="S206" t="inlineStr"/>
       <c r="T206" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="U206" t="inlineStr"/>
+        <v>46177</v>
+      </c>
+      <c r="U206" s="3" t="n">
+        <v>46200</v>
+      </c>
       <c r="V206" t="inlineStr"/>
       <c r="W206" t="inlineStr"/>
       <c r="X206" t="inlineStr"/>
@@ -17791,6 +17945,1154 @@
       <c r="AA206" t="inlineStr"/>
       <c r="AB206" t="inlineStr">
         <is>
+          <t>SISTEMAS AUXILIARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>0</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>GO/53-226-SA-1</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>5017897</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>TUBERIAS</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>0080</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Cambio de columna barometrica</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>3200</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="n">
+        <v>30020813</v>
+      </c>
+      <c r="N207" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O207" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="inlineStr"/>
+      <c r="T207" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="U207" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="V207" t="inlineStr"/>
+      <c r="W207" t="inlineStr"/>
+      <c r="X207" t="inlineStr"/>
+      <c r="Y207" t="inlineStr"/>
+      <c r="Z207" t="inlineStr"/>
+      <c r="AA207" t="inlineStr"/>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>SISTEMAS AUXILIARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>0</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>GO/53-226-PM</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>5017898</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>TANQUE AGUAS SUCIAS</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Instalalacion de tuberias de descarga</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="n">
+        <v>30020814</v>
+      </c>
+      <c r="N208" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O208" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="inlineStr"/>
+      <c r="T208" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="U208" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="V208" t="inlineStr"/>
+      <c r="W208" t="inlineStr"/>
+      <c r="X208" t="inlineStr"/>
+      <c r="Y208" t="inlineStr"/>
+      <c r="Z208" t="inlineStr"/>
+      <c r="AA208" t="inlineStr"/>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>PROYECTO MEJORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>0</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>GO/53-226-PM</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>5017898</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>TANQUE AGUAS SUCIAS</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Instalacion de tuberias de llenado</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="n">
+        <v>30020814</v>
+      </c>
+      <c r="N209" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O209" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="inlineStr"/>
+      <c r="T209" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="U209" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="V209" t="inlineStr"/>
+      <c r="W209" t="inlineStr"/>
+      <c r="X209" t="inlineStr"/>
+      <c r="Y209" t="inlineStr"/>
+      <c r="Z209" t="inlineStr"/>
+      <c r="AA209" t="inlineStr"/>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>PROYECTO MEJORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>0</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>GO/53-226-PM</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>5017898</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>TANQUE AGUAS SUCIAS</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Confeccion/Instalacion de base ebba</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>3200</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="n">
+        <v>30020814</v>
+      </c>
+      <c r="N210" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O210" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="inlineStr"/>
+      <c r="T210" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="U210" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="V210" t="inlineStr"/>
+      <c r="W210" t="inlineStr"/>
+      <c r="X210" t="inlineStr"/>
+      <c r="Y210" t="inlineStr"/>
+      <c r="Z210" t="inlineStr"/>
+      <c r="AA210" t="inlineStr"/>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>PROYECTO MEJORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>0</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>GO/53-226-PM</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>5017899</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>TANQUE MEZCLAS OLEOSAS</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Confeccion de tanque de mezclas oleosas</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="n">
+        <v>30020815</v>
+      </c>
+      <c r="N211" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O211" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="inlineStr"/>
+      <c r="T211" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="U211" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="V211" t="inlineStr"/>
+      <c r="W211" t="inlineStr"/>
+      <c r="X211" t="inlineStr"/>
+      <c r="Y211" t="inlineStr"/>
+      <c r="Z211" t="inlineStr"/>
+      <c r="AA211" t="inlineStr"/>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>PROYECTO MEJORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>0</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>GO/53-226-PM</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>5017899</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>TANQUE MEZCLAS OLEOSAS</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Instalalacion de tuberias de descarga</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="n">
+        <v>30020815</v>
+      </c>
+      <c r="N212" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O212" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="inlineStr"/>
+      <c r="T212" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="U212" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="V212" t="inlineStr"/>
+      <c r="W212" t="inlineStr"/>
+      <c r="X212" t="inlineStr"/>
+      <c r="Y212" t="inlineStr"/>
+      <c r="Z212" t="inlineStr"/>
+      <c r="AA212" t="inlineStr"/>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>PROYECTO MEJORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>0</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>GO/53-226-PM</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>5017899</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>TANQUE MEZCLAS OLEOSAS</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Instalacion de tuberias de llenado</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="n">
+        <v>30020815</v>
+      </c>
+      <c r="N213" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O213" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="inlineStr"/>
+      <c r="T213" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="U213" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="V213" t="inlineStr"/>
+      <c r="W213" t="inlineStr"/>
+      <c r="X213" t="inlineStr"/>
+      <c r="Y213" t="inlineStr"/>
+      <c r="Z213" t="inlineStr"/>
+      <c r="AA213" t="inlineStr"/>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>PROYECTO MEJORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>0</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>GO/53-226-PM</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>5017899</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>TANQUE MEZCLAS OLEOSAS</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Confeccion/Instalacion de base ebba</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>3200</v>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="n">
+        <v>30020815</v>
+      </c>
+      <c r="N214" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O214" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" t="inlineStr"/>
+      <c r="T214" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="U214" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="V214" t="inlineStr"/>
+      <c r="W214" t="inlineStr"/>
+      <c r="X214" t="inlineStr"/>
+      <c r="Y214" t="inlineStr"/>
+      <c r="Z214" t="inlineStr"/>
+      <c r="AA214" t="inlineStr"/>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>PROYECTO MEJORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>0</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>GO/53-226-TS-1</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>5017900</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>TRATAMIENTOS</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Arenado y pintado</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>46000</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="n">
+        <v>30020816</v>
+      </c>
+      <c r="N215" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O215" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="inlineStr"/>
+      <c r="T215" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="U215" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="V215" t="inlineStr"/>
+      <c r="W215" t="inlineStr"/>
+      <c r="X215" t="inlineStr"/>
+      <c r="Y215" t="inlineStr"/>
+      <c r="Z215" t="inlineStr"/>
+      <c r="AA215" t="inlineStr"/>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>TRATAMIENTO SUPERFICIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>0</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>GO/53-226-BM</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>5017901</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>BOMBAS</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Confección de base de bomba refrigerac</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>2400</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="n">
+        <v>30020817</v>
+      </c>
+      <c r="N216" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O216" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" t="inlineStr"/>
+      <c r="T216" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="U216" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="V216" t="inlineStr"/>
+      <c r="W216" t="inlineStr"/>
+      <c r="X216" t="inlineStr"/>
+      <c r="Y216" t="inlineStr"/>
+      <c r="Z216" t="inlineStr"/>
+      <c r="AA216" t="inlineStr"/>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>BOMBAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>0</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>GO/53-226-BM</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>5017901</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>BOMBAS</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Confección de base de bomba autocebante</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>2400</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="n">
+        <v>30020817</v>
+      </c>
+      <c r="N217" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O217" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" t="inlineStr"/>
+      <c r="T217" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="U217" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="V217" t="inlineStr"/>
+      <c r="W217" t="inlineStr"/>
+      <c r="X217" t="inlineStr"/>
+      <c r="Y217" t="inlineStr"/>
+      <c r="Z217" t="inlineStr"/>
+      <c r="AA217" t="inlineStr"/>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>BOMBAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>0</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>GO/53-226-BM</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>5017901</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>BOMBAS</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Inst de bba refrigeracion</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="n">
+        <v>30020817</v>
+      </c>
+      <c r="N218" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O218" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="n">
+        <v>0</v>
+      </c>
+      <c r="S218" t="inlineStr"/>
+      <c r="T218" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="U218" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="V218" t="inlineStr"/>
+      <c r="W218" t="inlineStr"/>
+      <c r="X218" t="inlineStr"/>
+      <c r="Y218" t="inlineStr"/>
+      <c r="Z218" t="inlineStr"/>
+      <c r="AA218" t="inlineStr"/>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>BOMBAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>0</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>GO/53-226-BM</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>5017901</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>BOMBAS</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Inst de bba autocebante</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="n">
+        <v>30020817</v>
+      </c>
+      <c r="N219" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O219" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
+      <c r="R219" t="n">
+        <v>0</v>
+      </c>
+      <c r="S219" t="inlineStr"/>
+      <c r="T219" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="U219" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="V219" t="inlineStr"/>
+      <c r="W219" t="inlineStr"/>
+      <c r="X219" t="inlineStr"/>
+      <c r="Y219" t="inlineStr"/>
+      <c r="Z219" t="inlineStr"/>
+      <c r="AA219" t="inlineStr"/>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>BOMBAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>0</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>CHATA TAMAKUN</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>GO/53</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>GO/53-226-CA-PI-4</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>5017902</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>ESFUERZO ADICIONAL</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Esfuerzo adicional</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="n">
+        <v>30020819</v>
+      </c>
+      <c r="N220" s="3" t="n">
+        <v>46178</v>
+      </c>
+      <c r="O220" s="3" t="n">
+        <v>46178</v>
+      </c>
+      <c r="P220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr"/>
+      <c r="R220" t="n">
+        <v>0</v>
+      </c>
+      <c r="S220" t="inlineStr"/>
+      <c r="T220" s="3" t="n">
+        <v>46178</v>
+      </c>
+      <c r="U220" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="V220" t="inlineStr"/>
+      <c r="W220" t="inlineStr"/>
+      <c r="X220" t="inlineStr"/>
+      <c r="Y220" t="inlineStr"/>
+      <c r="Z220" t="inlineStr"/>
+      <c r="AA220" t="inlineStr"/>
+      <c r="AB220" t="inlineStr">
+        <is>
           <t>CASCO</t>
         </is>
       </c>

--- a/2026-2/UTI.xlsx
+++ b/2026-2/UTI.xlsx
@@ -48779,7 +48779,7 @@
       <c r="AA532" t="inlineStr"/>
       <c r="AB532" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -48861,7 +48861,7 @@
       <c r="AA533" t="inlineStr"/>
       <c r="AB533" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -48943,7 +48943,7 @@
       <c r="AA534" t="inlineStr"/>
       <c r="AB534" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -49025,7 +49025,7 @@
       <c r="AA535" t="inlineStr"/>
       <c r="AB535" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -49107,7 +49107,7 @@
       <c r="AA536" t="inlineStr"/>
       <c r="AB536" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -49189,7 +49189,7 @@
       <c r="AA537" t="inlineStr"/>
       <c r="AB537" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -49271,7 +49271,7 @@
       <c r="AA538" t="inlineStr"/>
       <c r="AB538" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -49359,7 +49359,7 @@
       </c>
       <c r="AB539" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -49447,7 +49447,7 @@
       </c>
       <c r="AB540" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -49535,7 +49535,7 @@
       </c>
       <c r="AB541" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -49623,7 +49623,7 @@
       </c>
       <c r="AB542" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -49711,7 +49711,7 @@
       </c>
       <c r="AB543" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -49799,7 +49799,7 @@
       </c>
       <c r="AB544" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -49881,7 +49881,7 @@
       <c r="AA545" t="inlineStr"/>
       <c r="AB545" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -49969,7 +49969,7 @@
       </c>
       <c r="AB546" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -50057,7 +50057,7 @@
       </c>
       <c r="AB547" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -50145,7 +50145,7 @@
       </c>
       <c r="AB548" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -50233,7 +50233,7 @@
       </c>
       <c r="AB549" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -50325,7 +50325,7 @@
       <c r="AA550" t="inlineStr"/>
       <c r="AB550" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>PROPULSION Y GOBIERNO</t>
         </is>
       </c>
     </row>
@@ -50417,7 +50417,7 @@
       <c r="AA551" t="inlineStr"/>
       <c r="AB551" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>PROPULSION Y GOBIERNO</t>
         </is>
       </c>
     </row>
@@ -50505,7 +50505,7 @@
       <c r="AA552" t="inlineStr"/>
       <c r="AB552" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>PROPULSION Y GOBIERNO</t>
         </is>
       </c>
     </row>
@@ -50599,7 +50599,7 @@
       </c>
       <c r="AB553" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>PROPULSION Y GOBIERNO</t>
         </is>
       </c>
     </row>
@@ -50687,7 +50687,7 @@
       <c r="AA554" t="inlineStr"/>
       <c r="AB554" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>PROPULSION Y GOBIERNO</t>
         </is>
       </c>
     </row>
@@ -53779,7 +53779,7 @@
       <c r="AA589" t="inlineStr"/>
       <c r="AB589" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>PROPULSION Y GOBIERNO</t>
         </is>
       </c>
     </row>
@@ -53871,7 +53871,7 @@
       <c r="AA590" t="inlineStr"/>
       <c r="AB590" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>PROPULSION Y GOBIERNO</t>
         </is>
       </c>
     </row>
@@ -53959,7 +53959,7 @@
       <c r="AA591" t="inlineStr"/>
       <c r="AB591" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>PROPULSION Y GOBIERNO</t>
         </is>
       </c>
     </row>
@@ -54047,7 +54047,7 @@
       <c r="AA592" t="inlineStr"/>
       <c r="AB592" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>PROPULSION Y GOBIERNO</t>
         </is>
       </c>
     </row>
@@ -55267,7 +55267,7 @@
       <c r="AA606" t="inlineStr"/>
       <c r="AB606" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>PROPULSION Y GOBIERNO</t>
         </is>
       </c>
     </row>
@@ -55361,7 +55361,7 @@
       </c>
       <c r="AB607" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -55449,7 +55449,7 @@
       <c r="AA608" t="inlineStr"/>
       <c r="AB608" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -56175,7 +56175,7 @@
       <c r="AA616" t="inlineStr"/>
       <c r="AB616" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -56273,7 +56273,7 @@
       <c r="AA617" t="inlineStr"/>
       <c r="AB617" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
@@ -56651,7 +56651,7 @@
       <c r="AA621" t="inlineStr"/>
       <c r="AB621" t="inlineStr">
         <is>
-          <t>CASCO</t>
+          <t>SISTEMAS AUXILIARES</t>
         </is>
       </c>
     </row>
